--- a/data/proteomics/total_protein_abundance_across_compartment_Rosemary_NH4_limitation_v2.xlsx
+++ b/data/proteomics/total_protein_abundance_across_compartment_Rosemary_NH4_limitation_v2.xlsx
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12572768.18005952</v>
+        <v>12572768.18005953</v>
       </c>
       <c r="D2" t="n">
-        <v>11458086.20441382</v>
+        <v>11458086.20441381</v>
       </c>
       <c r="E2" t="n">
-        <v>12480358.28212649</v>
+        <v>12480358.28212648</v>
       </c>
       <c r="F2" t="n">
-        <v>9804834.523530224</v>
+        <v>9804834.523530221</v>
       </c>
       <c r="G2" t="n">
-        <v>10233657.9139681</v>
+        <v>10233657.91396813</v>
       </c>
       <c r="H2" t="n">
-        <v>14048836.82346556</v>
+        <v>14048836.82346555</v>
       </c>
       <c r="I2" t="n">
         <v>14995790.64073839</v>
@@ -559,34 +559,34 @@
         <v>12949145.23843527</v>
       </c>
       <c r="K2" t="n">
-        <v>13080325.10668174</v>
+        <v>13080325.10668173</v>
       </c>
       <c r="L2" t="n">
-        <v>13961900.49088705</v>
+        <v>13961900.49088704</v>
       </c>
       <c r="M2" t="n">
         <v>13869762.42542628</v>
       </c>
       <c r="N2" t="n">
-        <v>14368694.77576886</v>
+        <v>14368694.77576887</v>
       </c>
       <c r="O2" t="n">
-        <v>24898765.03929793</v>
+        <v>24898765.03929792</v>
       </c>
       <c r="P2" t="n">
-        <v>25061750.18739839</v>
+        <v>25061750.18739838</v>
       </c>
       <c r="Q2" t="n">
-        <v>23020284.37370481</v>
+        <v>23020284.3737048</v>
       </c>
       <c r="R2" t="n">
-        <v>30634398.22577013</v>
+        <v>30634398.22577012</v>
       </c>
       <c r="S2" t="n">
         <v>32532632.01617341</v>
       </c>
       <c r="T2" t="n">
-        <v>32501505.84830231</v>
+        <v>32501505.84830233</v>
       </c>
     </row>
     <row r="3">
@@ -608,7 +608,7 @@
         <v>16496.12730428639</v>
       </c>
       <c r="F3" t="n">
-        <v>14194.05074710816</v>
+        <v>14194.05074710817</v>
       </c>
       <c r="G3" t="n">
         <v>14820.02086780136</v>
@@ -632,7 +632,7 @@
         <v>18198.50771221998</v>
       </c>
       <c r="N3" t="n">
-        <v>19967.69255497185</v>
+        <v>19967.69255497184</v>
       </c>
       <c r="O3" t="n">
         <v>25773.60003580783</v>
@@ -669,7 +669,7 @@
         <v>18403.19275952498</v>
       </c>
       <c r="E4" t="n">
-        <v>22645.68413364699</v>
+        <v>22645.684133647</v>
       </c>
       <c r="F4" t="n">
         <v>22453.67539625895</v>
@@ -678,43 +678,43 @@
         <v>22335.20225453324</v>
       </c>
       <c r="H4" t="n">
-        <v>20519.96133009177</v>
+        <v>20519.96133009176</v>
       </c>
       <c r="I4" t="n">
         <v>32966.3646550023</v>
       </c>
       <c r="J4" t="n">
-        <v>28304.71522271363</v>
+        <v>28304.71522271364</v>
       </c>
       <c r="K4" t="n">
-        <v>23650.38615903434</v>
+        <v>23650.38615903433</v>
       </c>
       <c r="L4" t="n">
-        <v>24297.36309276656</v>
+        <v>24297.36309276657</v>
       </c>
       <c r="M4" t="n">
         <v>34446.38383036337</v>
       </c>
       <c r="N4" t="n">
-        <v>34631.51852854585</v>
+        <v>34631.51852854586</v>
       </c>
       <c r="O4" t="n">
-        <v>48742.1373387062</v>
+        <v>48742.13733870621</v>
       </c>
       <c r="P4" t="n">
-        <v>57243.60757594915</v>
+        <v>57243.60757594914</v>
       </c>
       <c r="Q4" t="n">
-        <v>54746.2072179906</v>
+        <v>54746.20721799062</v>
       </c>
       <c r="R4" t="n">
-        <v>63338.78980380233</v>
+        <v>63338.7898038023</v>
       </c>
       <c r="S4" t="n">
-        <v>74910.83847556652</v>
+        <v>74910.83847556649</v>
       </c>
       <c r="T4" t="n">
-        <v>76863.39621142301</v>
+        <v>76863.39621142302</v>
       </c>
     </row>
     <row r="5">
@@ -791,58 +791,58 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7832577.05401173</v>
+        <v>7832577.054011728</v>
       </c>
       <c r="D6" t="n">
-        <v>7169623.402250009</v>
+        <v>7169623.402250002</v>
       </c>
       <c r="E6" t="n">
-        <v>8083380.265122569</v>
+        <v>8083380.265122568</v>
       </c>
       <c r="F6" t="n">
         <v>6220786.411007226</v>
       </c>
       <c r="G6" t="n">
-        <v>6527731.098884046</v>
+        <v>6527731.098884043</v>
       </c>
       <c r="H6" t="n">
-        <v>8875061.306705425</v>
+        <v>8875061.306705398</v>
       </c>
       <c r="I6" t="n">
         <v>9241572.712384328</v>
       </c>
       <c r="J6" t="n">
-        <v>8165407.020044643</v>
+        <v>8165407.020044641</v>
       </c>
       <c r="K6" t="n">
-        <v>7996266.039167041</v>
+        <v>7996266.039167034</v>
       </c>
       <c r="L6" t="n">
-        <v>8265809.759184134</v>
+        <v>8265809.759184131</v>
       </c>
       <c r="M6" t="n">
-        <v>8453059.812679751</v>
+        <v>8453059.812679738</v>
       </c>
       <c r="N6" t="n">
-        <v>8789426.605140164</v>
+        <v>8789426.605140183</v>
       </c>
       <c r="O6" t="n">
-        <v>15509610.67275534</v>
+        <v>15509610.67275535</v>
       </c>
       <c r="P6" t="n">
-        <v>15877643.66789918</v>
+        <v>15877643.66789919</v>
       </c>
       <c r="Q6" t="n">
-        <v>14693928.28335695</v>
+        <v>14693928.28335692</v>
       </c>
       <c r="R6" t="n">
-        <v>20248122.39564364</v>
+        <v>20248122.39564366</v>
       </c>
       <c r="S6" t="n">
-        <v>21655335.60406316</v>
+        <v>21655335.6040632</v>
       </c>
       <c r="T6" t="n">
-        <v>20836009.5274046</v>
+        <v>20836009.52740457</v>
       </c>
     </row>
     <row r="7">
@@ -855,58 +855,58 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16420534.75090745</v>
+        <v>16420534.75090747</v>
       </c>
       <c r="D7" t="n">
         <v>14868704.87134332</v>
       </c>
       <c r="E7" t="n">
-        <v>15716615.48192729</v>
+        <v>15716615.48192728</v>
       </c>
       <c r="F7" t="n">
-        <v>12868144.47496249</v>
+        <v>12868144.4749625</v>
       </c>
       <c r="G7" t="n">
         <v>13568248.00336507</v>
       </c>
       <c r="H7" t="n">
-        <v>18999443.71927822</v>
+        <v>18999443.7192782</v>
       </c>
       <c r="I7" t="n">
-        <v>20376002.11991398</v>
+        <v>20376002.11991395</v>
       </c>
       <c r="J7" t="n">
-        <v>17299654.96875937</v>
+        <v>17299654.96875939</v>
       </c>
       <c r="K7" t="n">
-        <v>17437305.433318</v>
+        <v>17437305.43331802</v>
       </c>
       <c r="L7" t="n">
-        <v>21445666.75661476</v>
+        <v>21445666.75661475</v>
       </c>
       <c r="M7" t="n">
-        <v>20782889.39912913</v>
+        <v>20782889.3991291</v>
       </c>
       <c r="N7" t="n">
-        <v>20332107.3650318</v>
+        <v>20332107.36503178</v>
       </c>
       <c r="O7" t="n">
-        <v>44380567.80811906</v>
+        <v>44380567.80811908</v>
       </c>
       <c r="P7" t="n">
         <v>44185708.95839284</v>
       </c>
       <c r="Q7" t="n">
-        <v>42089543.67861601</v>
+        <v>42089543.67861609</v>
       </c>
       <c r="R7" t="n">
-        <v>61480768.11416873</v>
+        <v>61480768.1141688</v>
       </c>
       <c r="S7" t="n">
-        <v>64796978.38643348</v>
+        <v>64796978.38643342</v>
       </c>
       <c r="T7" t="n">
-        <v>63960833.03894603</v>
+        <v>63960833.03894592</v>
       </c>
     </row>
     <row r="8">
@@ -919,40 +919,40 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7051314.85742232</v>
+        <v>7051314.857422318</v>
       </c>
       <c r="D8" t="n">
-        <v>6181949.968102738</v>
+        <v>6181949.968102737</v>
       </c>
       <c r="E8" t="n">
-        <v>6234000.346070281</v>
+        <v>6234000.346070284</v>
       </c>
       <c r="F8" t="n">
-        <v>5479222.485814325</v>
+        <v>5479222.485814322</v>
       </c>
       <c r="G8" t="n">
-        <v>5650286.810039187</v>
+        <v>5650286.810039188</v>
       </c>
       <c r="H8" t="n">
-        <v>8226509.692449612</v>
+        <v>8226509.69244961</v>
       </c>
       <c r="I8" t="n">
-        <v>8341630.51712811</v>
+        <v>8341630.517128108</v>
       </c>
       <c r="J8" t="n">
-        <v>7370510.471691669</v>
+        <v>7370510.471691667</v>
       </c>
       <c r="K8" t="n">
-        <v>7242789.16763582</v>
+        <v>7242789.167635814</v>
       </c>
       <c r="L8" t="n">
-        <v>7045686.841543518</v>
+        <v>7045686.841543521</v>
       </c>
       <c r="M8" t="n">
-        <v>7238375.632680828</v>
+        <v>7238375.632680827</v>
       </c>
       <c r="N8" t="n">
-        <v>7336217.080984169</v>
+        <v>7336217.080984168</v>
       </c>
       <c r="O8" t="n">
         <v>13882426.00490013</v>
@@ -961,13 +961,13 @@
         <v>13812420.57729954</v>
       </c>
       <c r="Q8" t="n">
-        <v>13220914.12289081</v>
+        <v>13220914.12289079</v>
       </c>
       <c r="R8" t="n">
-        <v>18446047.92997856</v>
+        <v>18446047.92997855</v>
       </c>
       <c r="S8" t="n">
-        <v>20287404.07787357</v>
+        <v>20287404.07787358</v>
       </c>
       <c r="T8" t="n">
         <v>18948863.69486476</v>
@@ -989,7 +989,7 @@
         <v>1315821.848117782</v>
       </c>
       <c r="E9" t="n">
-        <v>1207012.705317596</v>
+        <v>1207012.705317595</v>
       </c>
       <c r="F9" t="n">
         <v>1053338.763183088</v>
@@ -998,7 +998,7 @@
         <v>1126319.703630694</v>
       </c>
       <c r="H9" t="n">
-        <v>1695173.305717827</v>
+        <v>1695173.305717828</v>
       </c>
       <c r="I9" t="n">
         <v>1575664.167325385</v>
@@ -1013,7 +1013,7 @@
         <v>1267621.790040578</v>
       </c>
       <c r="M9" t="n">
-        <v>1259891.970066819</v>
+        <v>1259891.97006682</v>
       </c>
       <c r="N9" t="n">
         <v>1104482.524647218</v>
@@ -1022,7 +1022,7 @@
         <v>2525244.388913415</v>
       </c>
       <c r="P9" t="n">
-        <v>2434399.114715705</v>
+        <v>2434399.114715704</v>
       </c>
       <c r="Q9" t="n">
         <v>2663363.351256039</v>
@@ -1031,7 +1031,7 @@
         <v>3785706.150528525</v>
       </c>
       <c r="S9" t="n">
-        <v>4189471.981773999</v>
+        <v>4189471.981773998</v>
       </c>
       <c r="T9" t="n">
         <v>3732323.099715129</v>
@@ -1126,13 +1126,13 @@
         <v>1750211.036340168</v>
       </c>
       <c r="H11" t="n">
-        <v>3426269.47738582</v>
+        <v>3426269.477385821</v>
       </c>
       <c r="I11" t="n">
         <v>2920706.787552329</v>
       </c>
       <c r="J11" t="n">
-        <v>2492281.384059919</v>
+        <v>2492281.384059918</v>
       </c>
       <c r="K11" t="n">
         <v>2508949.625800086</v>
@@ -1147,22 +1147,22 @@
         <v>2058471.842387928</v>
       </c>
       <c r="O11" t="n">
-        <v>4720372.328943907</v>
+        <v>4720372.328943909</v>
       </c>
       <c r="P11" t="n">
-        <v>4790239.573850557</v>
+        <v>4790239.573850558</v>
       </c>
       <c r="Q11" t="n">
         <v>4732974.047995347</v>
       </c>
       <c r="R11" t="n">
-        <v>6757837.853425839</v>
+        <v>6757837.853425837</v>
       </c>
       <c r="S11" t="n">
-        <v>8461998.315023182</v>
+        <v>8461998.31502318</v>
       </c>
       <c r="T11" t="n">
-        <v>7103039.488509315</v>
+        <v>7103039.488509314</v>
       </c>
     </row>
     <row r="12">
@@ -1175,25 +1175,25 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>879059.0427540807</v>
+        <v>879059.0427540811</v>
       </c>
       <c r="D12" t="n">
-        <v>797605.1024102009</v>
+        <v>797605.1024101999</v>
       </c>
       <c r="E12" t="n">
-        <v>771007.4412993022</v>
+        <v>771007.4412993019</v>
       </c>
       <c r="F12" t="n">
-        <v>716398.9914600491</v>
+        <v>716398.9914600495</v>
       </c>
       <c r="G12" t="n">
-        <v>788039.9562849129</v>
+        <v>788039.9562849123</v>
       </c>
       <c r="H12" t="n">
-        <v>757758.2649012693</v>
+        <v>757758.2649012695</v>
       </c>
       <c r="I12" t="n">
-        <v>1165488.809137967</v>
+        <v>1165488.809137968</v>
       </c>
       <c r="J12" t="n">
         <v>976935.6850763356</v>
@@ -1202,31 +1202,31 @@
         <v>1053430.86357752</v>
       </c>
       <c r="L12" t="n">
-        <v>1195499.652081751</v>
+        <v>1195499.652081752</v>
       </c>
       <c r="M12" t="n">
-        <v>1107832.268952915</v>
+        <v>1107832.268952914</v>
       </c>
       <c r="N12" t="n">
         <v>1186425.321273628</v>
       </c>
       <c r="O12" t="n">
-        <v>1856146.623722492</v>
+        <v>1856146.62372249</v>
       </c>
       <c r="P12" t="n">
         <v>1899948.828591129</v>
       </c>
       <c r="Q12" t="n">
-        <v>1832068.261112978</v>
+        <v>1832068.261112977</v>
       </c>
       <c r="R12" t="n">
-        <v>2165508.931335453</v>
+        <v>2165508.931335454</v>
       </c>
       <c r="S12" t="n">
         <v>2414923.465383987</v>
       </c>
       <c r="T12" t="n">
-        <v>2503315.876500125</v>
+        <v>2503315.876500126</v>
       </c>
     </row>
     <row r="13">
@@ -1239,22 +1239,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>99494.9757078913</v>
+        <v>99494.97570789131</v>
       </c>
       <c r="D13" t="n">
         <v>86936.87621886902</v>
       </c>
       <c r="E13" t="n">
-        <v>88698.21170671185</v>
+        <v>88698.21170671184</v>
       </c>
       <c r="F13" t="n">
-        <v>91842.82129299013</v>
+        <v>91842.82129299011</v>
       </c>
       <c r="G13" t="n">
         <v>102330.4607673589</v>
       </c>
       <c r="H13" t="n">
-        <v>82843.07450670224</v>
+        <v>82843.07450670225</v>
       </c>
       <c r="I13" t="n">
         <v>159114.3001179835</v>
@@ -1275,7 +1275,7 @@
         <v>165200.1682951966</v>
       </c>
       <c r="O13" t="n">
-        <v>238443.2664915843</v>
+        <v>238443.2664915844</v>
       </c>
       <c r="P13" t="n">
         <v>216985.4994374251</v>
@@ -1303,49 +1303,49 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>627866.4735660874</v>
+        <v>627866.4735660872</v>
       </c>
       <c r="D14" t="n">
         <v>619182.5460985287</v>
       </c>
       <c r="E14" t="n">
-        <v>714350.721858367</v>
+        <v>714350.7218583666</v>
       </c>
       <c r="F14" t="n">
-        <v>467560.0153653232</v>
+        <v>467560.015365323</v>
       </c>
       <c r="G14" t="n">
-        <v>541450.6437176019</v>
+        <v>541450.643717602</v>
       </c>
       <c r="H14" t="n">
-        <v>695172.1112875263</v>
+        <v>695172.1112875262</v>
       </c>
       <c r="I14" t="n">
-        <v>814106.6706300429</v>
+        <v>814106.6706300431</v>
       </c>
       <c r="J14" t="n">
         <v>691135.097499758</v>
       </c>
       <c r="K14" t="n">
-        <v>670494.336777825</v>
+        <v>670494.3367778256</v>
       </c>
       <c r="L14" t="n">
-        <v>733394.0884303198</v>
+        <v>733394.08843032</v>
       </c>
       <c r="M14" t="n">
-        <v>692284.1914306583</v>
+        <v>692284.1914306587</v>
       </c>
       <c r="N14" t="n">
         <v>760046.0203204445</v>
       </c>
       <c r="O14" t="n">
-        <v>1041589.521358891</v>
+        <v>1041589.521358892</v>
       </c>
       <c r="P14" t="n">
         <v>1071843.383650246</v>
       </c>
       <c r="Q14" t="n">
-        <v>933774.5704153045</v>
+        <v>933774.5704153046</v>
       </c>
       <c r="R14" t="n">
         <v>1126232.70932849</v>
@@ -1354,7 +1354,7 @@
         <v>1229367.150928699</v>
       </c>
       <c r="T14" t="n">
-        <v>1232484.137496036</v>
+        <v>1232484.137496035</v>
       </c>
     </row>
     <row r="15">
@@ -1373,13 +1373,13 @@
         <v>103152.7140064969</v>
       </c>
       <c r="E15" t="n">
-        <v>106119.6916699286</v>
+        <v>106119.6916699285</v>
       </c>
       <c r="F15" t="n">
-        <v>88406.36427359931</v>
+        <v>88406.36427359932</v>
       </c>
       <c r="G15" t="n">
-        <v>97044.46844583683</v>
+        <v>97044.46844583684</v>
       </c>
       <c r="H15" t="n">
         <v>195890.744613808</v>
@@ -1391,13 +1391,13 @@
         <v>179027.4941893611</v>
       </c>
       <c r="K15" t="n">
-        <v>163218.2719809583</v>
+        <v>163218.2719809584</v>
       </c>
       <c r="L15" t="n">
         <v>171852.5735197635</v>
       </c>
       <c r="M15" t="n">
-        <v>156674.3592334224</v>
+        <v>156674.3592334225</v>
       </c>
       <c r="N15" t="n">
         <v>174720.657335575</v>
@@ -1406,7 +1406,7 @@
         <v>260227.536640607</v>
       </c>
       <c r="P15" t="n">
-        <v>308121.9425265714</v>
+        <v>308121.9425265713</v>
       </c>
       <c r="Q15" t="n">
         <v>241537.4927579546</v>
@@ -1437,7 +1437,7 @@
         <v>148084.834549444</v>
       </c>
       <c r="E16" t="n">
-        <v>138287.7612755528</v>
+        <v>138287.7612755529</v>
       </c>
       <c r="F16" t="n">
         <v>145324.2158718807</v>
@@ -1446,7 +1446,7 @@
         <v>147485.0376340396</v>
       </c>
       <c r="H16" t="n">
-        <v>99111.29095064156</v>
+        <v>99111.29095064157</v>
       </c>
       <c r="I16" t="n">
         <v>203435.1349689339</v>
@@ -1461,7 +1461,7 @@
         <v>206635.185639852</v>
       </c>
       <c r="M16" t="n">
-        <v>201347.7714220325</v>
+        <v>201347.7714220324</v>
       </c>
       <c r="N16" t="n">
         <v>217848.7043998762</v>
@@ -1470,13 +1470,13 @@
         <v>279203.0067719481</v>
       </c>
       <c r="P16" t="n">
-        <v>277599.9223736779</v>
+        <v>277599.922373678</v>
       </c>
       <c r="Q16" t="n">
-        <v>270618.0231873356</v>
+        <v>270618.0231873355</v>
       </c>
       <c r="R16" t="n">
-        <v>281219.4572514471</v>
+        <v>281219.457251447</v>
       </c>
       <c r="S16" t="n">
         <v>284276.030023589</v>
@@ -1504,7 +1504,7 @@
         <v>227057.7703389899</v>
       </c>
       <c r="F17" t="n">
-        <v>208698.9161803091</v>
+        <v>208698.9161803092</v>
       </c>
       <c r="G17" t="n">
         <v>240709.7753508453</v>
@@ -1513,10 +1513,10 @@
         <v>249343.5629922259</v>
       </c>
       <c r="I17" t="n">
-        <v>415839.242362313</v>
+        <v>415839.2423623129</v>
       </c>
       <c r="J17" t="n">
-        <v>345961.5360338899</v>
+        <v>345961.53603389</v>
       </c>
       <c r="K17" t="n">
         <v>190644.2445900156</v>
@@ -1528,16 +1528,16 @@
         <v>372081.8372274569</v>
       </c>
       <c r="N17" t="n">
-        <v>393164.5158790819</v>
+        <v>393164.515879082</v>
       </c>
       <c r="O17" t="n">
         <v>227684.7637636946</v>
       </c>
       <c r="P17" t="n">
-        <v>623509.8449517167</v>
+        <v>623509.8449517168</v>
       </c>
       <c r="Q17" t="n">
-        <v>538413.906913736</v>
+        <v>538413.9069137361</v>
       </c>
       <c r="R17" t="n">
         <v>655768.7494149745</v>
@@ -1546,7 +1546,7 @@
         <v>682180.1066542061</v>
       </c>
       <c r="T17" t="n">
-        <v>683812.0517645302</v>
+        <v>683812.05176453</v>
       </c>
     </row>
     <row r="18">
@@ -1559,16 +1559,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>235412.6763247315</v>
+        <v>235412.6763247316</v>
       </c>
       <c r="D18" t="n">
-        <v>206217.0450643282</v>
+        <v>206217.0450643281</v>
       </c>
       <c r="E18" t="n">
         <v>192668.140677329</v>
       </c>
       <c r="F18" t="n">
-        <v>181692.4014801785</v>
+        <v>181692.4014801784</v>
       </c>
       <c r="G18" t="n">
         <v>201431.9793353997</v>
@@ -1577,7 +1577,7 @@
         <v>177288.4707716497</v>
       </c>
       <c r="I18" t="n">
-        <v>300064.2373799081</v>
+        <v>300064.2373799082</v>
       </c>
       <c r="J18" t="n">
         <v>238712.8820568381</v>
@@ -1586,16 +1586,16 @@
         <v>281998.6713843303</v>
       </c>
       <c r="L18" t="n">
-        <v>307398.7242048471</v>
+        <v>307398.7242048473</v>
       </c>
       <c r="M18" t="n">
-        <v>293554.6122365325</v>
+        <v>293554.6122365326</v>
       </c>
       <c r="N18" t="n">
-        <v>300389.0441118426</v>
+        <v>300389.0441118425</v>
       </c>
       <c r="O18" t="n">
-        <v>506802.2600775326</v>
+        <v>506802.2600775329</v>
       </c>
       <c r="P18" t="n">
         <v>511827.8977064496</v>
@@ -1604,13 +1604,13 @@
         <v>470164.7803402041</v>
       </c>
       <c r="R18" t="n">
-        <v>625492.2495755641</v>
+        <v>625492.2495755639</v>
       </c>
       <c r="S18" t="n">
-        <v>771573.9101228262</v>
+        <v>771573.9101228265</v>
       </c>
       <c r="T18" t="n">
-        <v>800467.2061494805</v>
+        <v>800467.2061494808</v>
       </c>
     </row>
     <row r="19">
@@ -1626,28 +1626,28 @@
         <v>76816.74742490529</v>
       </c>
       <c r="D19" t="n">
-        <v>68272.63198660777</v>
+        <v>68272.63198660778</v>
       </c>
       <c r="E19" t="n">
-        <v>69369.72131111581</v>
+        <v>69369.72131111582</v>
       </c>
       <c r="F19" t="n">
         <v>65043.18832763513</v>
       </c>
       <c r="G19" t="n">
-        <v>67787.25637667316</v>
+        <v>67787.25637667312</v>
       </c>
       <c r="H19" t="n">
-        <v>82477.37195837956</v>
+        <v>82477.37195837959</v>
       </c>
       <c r="I19" t="n">
         <v>111610.1427223132</v>
       </c>
       <c r="J19" t="n">
-        <v>97120.55167087041</v>
+        <v>97120.55167087038</v>
       </c>
       <c r="K19" t="n">
-        <v>96115.6483545271</v>
+        <v>96115.64835452707</v>
       </c>
       <c r="L19" t="n">
         <v>109183.0726779917</v>
@@ -1659,22 +1659,22 @@
         <v>104791.4883270106</v>
       </c>
       <c r="O19" t="n">
-        <v>180734.152071123</v>
+        <v>180734.1520711231</v>
       </c>
       <c r="P19" t="n">
         <v>180770.2335854053</v>
       </c>
       <c r="Q19" t="n">
-        <v>161651.1610411869</v>
+        <v>161651.1610411868</v>
       </c>
       <c r="R19" t="n">
-        <v>240857.5773316897</v>
+        <v>240857.5773316898</v>
       </c>
       <c r="S19" t="n">
-        <v>258930.824908514</v>
+        <v>258930.8249085138</v>
       </c>
       <c r="T19" t="n">
-        <v>246713.1906080966</v>
+        <v>246713.1906080965</v>
       </c>
     </row>
     <row r="20">
@@ -1693,52 +1693,52 @@
         <v>204423.370915674</v>
       </c>
       <c r="E20" t="n">
-        <v>226986.7128098704</v>
+        <v>226986.7128098705</v>
       </c>
       <c r="F20" t="n">
         <v>210590.3051702056</v>
       </c>
       <c r="G20" t="n">
-        <v>227812.3374208052</v>
+        <v>227812.3374208051</v>
       </c>
       <c r="H20" t="n">
-        <v>288480.3053711745</v>
+        <v>288480.3053711744</v>
       </c>
       <c r="I20" t="n">
-        <v>343904.520649281</v>
+        <v>343904.5206492812</v>
       </c>
       <c r="J20" t="n">
         <v>296318.1001044381</v>
       </c>
       <c r="K20" t="n">
-        <v>300687.0148028507</v>
+        <v>300687.0148028508</v>
       </c>
       <c r="L20" t="n">
         <v>371599.6785083862</v>
       </c>
       <c r="M20" t="n">
-        <v>373664.2916912661</v>
+        <v>373664.2916912659</v>
       </c>
       <c r="N20" t="n">
-        <v>331647.8647034243</v>
+        <v>331647.864703424</v>
       </c>
       <c r="O20" t="n">
-        <v>731791.9154172387</v>
+        <v>731791.9154172388</v>
       </c>
       <c r="P20" t="n">
-        <v>712399.1824456173</v>
+        <v>712399.1824456168</v>
       </c>
       <c r="Q20" t="n">
-        <v>680495.1962047456</v>
+        <v>680495.1962047457</v>
       </c>
       <c r="R20" t="n">
         <v>901447.1919128177</v>
       </c>
       <c r="S20" t="n">
-        <v>842598.1329136095</v>
+        <v>842598.1329136102</v>
       </c>
       <c r="T20" t="n">
-        <v>955213.4130096477</v>
+        <v>955213.4130096475</v>
       </c>
     </row>
     <row r="21">
@@ -1815,13 +1815,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>25161.92457658103</v>
+        <v>25161.92457658102</v>
       </c>
       <c r="D22" t="n">
-        <v>23038.25015442629</v>
+        <v>23038.2501544263</v>
       </c>
       <c r="E22" t="n">
-        <v>22423.20017880436</v>
+        <v>22423.20017880437</v>
       </c>
       <c r="F22" t="n">
         <v>18696.68757532473</v>
@@ -1842,16 +1842,16 @@
         <v>28696.58499776572</v>
       </c>
       <c r="L22" t="n">
-        <v>32377.73675910765</v>
+        <v>32377.73675910764</v>
       </c>
       <c r="M22" t="n">
         <v>31817.28514003101</v>
       </c>
       <c r="N22" t="n">
-        <v>34563.04969229028</v>
+        <v>34563.04969229027</v>
       </c>
       <c r="O22" t="n">
-        <v>54798.90090112541</v>
+        <v>54798.9009011254</v>
       </c>
       <c r="P22" t="n">
         <v>58207.00762990789</v>
@@ -1866,7 +1866,7 @@
         <v>71096.38759684634</v>
       </c>
       <c r="T22" t="n">
-        <v>72509.338784375</v>
+        <v>72509.33878437501</v>
       </c>
     </row>
     <row r="23">
@@ -1888,13 +1888,13 @@
         <v>1109706.759127511</v>
       </c>
       <c r="F23" t="n">
-        <v>937115.8318636416</v>
+        <v>937115.8318636417</v>
       </c>
       <c r="G23" t="n">
         <v>886619.0297748601</v>
       </c>
       <c r="H23" t="n">
-        <v>2435226.912740776</v>
+        <v>2435226.912740777</v>
       </c>
       <c r="I23" t="n">
         <v>1917298.706940042</v>
@@ -1915,7 +1915,7 @@
         <v>1333175.797985281</v>
       </c>
       <c r="O23" t="n">
-        <v>2853629.466310727</v>
+        <v>2853629.466310728</v>
       </c>
       <c r="P23" t="n">
         <v>2954657.78756263</v>
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6124.157818673965</v>
+        <v>6124.157818673966</v>
       </c>
       <c r="D24" t="n">
         <v>6304.986106189983</v>
@@ -1952,13 +1952,13 @@
         <v>6929.30150607956</v>
       </c>
       <c r="F24" t="n">
-        <v>6483.496825280187</v>
+        <v>6483.496825280188</v>
       </c>
       <c r="G24" t="n">
         <v>6173.891527387335</v>
       </c>
       <c r="H24" t="n">
-        <v>8265.656541826493</v>
+        <v>8265.656541826491</v>
       </c>
       <c r="I24" t="n">
         <v>11414.49090255837</v>
@@ -1979,7 +1979,7 @@
         <v>10689.30771116153</v>
       </c>
       <c r="O24" t="n">
-        <v>19959.36300864322</v>
+        <v>19959.36300864321</v>
       </c>
       <c r="P24" t="n">
         <v>18809.46009896431</v>
@@ -2007,25 +2007,25 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>91712.0744083491</v>
+        <v>91712.07440834909</v>
       </c>
       <c r="D25" t="n">
-        <v>82892.46469683523</v>
+        <v>82892.46469683528</v>
       </c>
       <c r="E25" t="n">
-        <v>86523.64137072637</v>
+        <v>86523.64137072636</v>
       </c>
       <c r="F25" t="n">
-        <v>73326.04689479695</v>
+        <v>73326.04689479693</v>
       </c>
       <c r="G25" t="n">
-        <v>81273.2009044461</v>
+        <v>81273.20090444613</v>
       </c>
       <c r="H25" t="n">
         <v>125777.8879722213</v>
       </c>
       <c r="I25" t="n">
-        <v>112959.4891412216</v>
+        <v>112959.4891412215</v>
       </c>
       <c r="J25" t="n">
         <v>101144.2783963095</v>
@@ -2046,10 +2046,10 @@
         <v>204647.629577765</v>
       </c>
       <c r="P25" t="n">
-        <v>208439.1261427831</v>
+        <v>208439.1261427832</v>
       </c>
       <c r="Q25" t="n">
-        <v>185977.1856584073</v>
+        <v>185977.1856584072</v>
       </c>
       <c r="R25" t="n">
         <v>229390.5624580041</v>
@@ -2058,7 +2058,7 @@
         <v>236161.3002481196</v>
       </c>
       <c r="T25" t="n">
-        <v>257638.7759187705</v>
+        <v>257638.7759187703</v>
       </c>
     </row>
     <row r="26">
@@ -2071,7 +2071,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>123211.4817348139</v>
+        <v>123211.4817348138</v>
       </c>
       <c r="D26" t="n">
         <v>115300.2728620581</v>
@@ -2086,7 +2086,7 @@
         <v>116707.0629750565</v>
       </c>
       <c r="H26" t="n">
-        <v>90800.65770070166</v>
+        <v>90800.65770070169</v>
       </c>
       <c r="I26" t="n">
         <v>179772.0908678857</v>
@@ -2098,16 +2098,16 @@
         <v>165012.235617364</v>
       </c>
       <c r="L26" t="n">
-        <v>188076.5039527228</v>
+        <v>188076.5039527227</v>
       </c>
       <c r="M26" t="n">
         <v>172819.2347474353</v>
       </c>
       <c r="N26" t="n">
-        <v>181057.8821910975</v>
+        <v>181057.8821910974</v>
       </c>
       <c r="O26" t="n">
-        <v>258950.6229799033</v>
+        <v>258950.6229799034</v>
       </c>
       <c r="P26" t="n">
         <v>246790.2559513251</v>
@@ -2116,10 +2116,10 @@
         <v>236806.8805542905</v>
       </c>
       <c r="R26" t="n">
-        <v>287353.8492520851</v>
+        <v>287353.8492520853</v>
       </c>
       <c r="S26" t="n">
-        <v>304168.3557320021</v>
+        <v>304168.3557320022</v>
       </c>
       <c r="T26" t="n">
         <v>362728.8443056251</v>
@@ -2141,13 +2141,13 @@
         <v>773759.0262252352</v>
       </c>
       <c r="E27" t="n">
-        <v>856607.8789307782</v>
+        <v>856607.8789307784</v>
       </c>
       <c r="F27" t="n">
-        <v>813181.9981639453</v>
+        <v>813181.9981639455</v>
       </c>
       <c r="G27" t="n">
-        <v>802624.7261504229</v>
+        <v>802624.7261504228</v>
       </c>
       <c r="H27" t="n">
         <v>1122474.629587292</v>
@@ -2171,22 +2171,22 @@
         <v>1462244.997880247</v>
       </c>
       <c r="O27" t="n">
-        <v>3521918.948926429</v>
+        <v>3521918.948926428</v>
       </c>
       <c r="P27" t="n">
-        <v>3778376.52545454</v>
+        <v>3778376.525454541</v>
       </c>
       <c r="Q27" t="n">
-        <v>3509249.76482559</v>
+        <v>3509249.764825589</v>
       </c>
       <c r="R27" t="n">
-        <v>5465740.092158559</v>
+        <v>5465740.092158557</v>
       </c>
       <c r="S27" t="n">
         <v>6004677.848870651</v>
       </c>
       <c r="T27" t="n">
-        <v>5806093.872348588</v>
+        <v>5806093.872348591</v>
       </c>
     </row>
     <row r="28">
@@ -2199,13 +2199,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>19029.51368182992</v>
+        <v>19029.51368182993</v>
       </c>
       <c r="D28" t="n">
         <v>17183.18394257211</v>
       </c>
       <c r="E28" t="n">
-        <v>21103.51530133643</v>
+        <v>21103.51530133644</v>
       </c>
       <c r="F28" t="n">
         <v>17883.09178756213</v>
@@ -2217,13 +2217,13 @@
         <v>19744.18149265807</v>
       </c>
       <c r="I28" t="n">
-        <v>25418.22522828857</v>
+        <v>25418.22522828856</v>
       </c>
       <c r="J28" t="n">
         <v>21735.07592543547</v>
       </c>
       <c r="K28" t="n">
-        <v>21802.83293784552</v>
+        <v>21802.83293784553</v>
       </c>
       <c r="L28" t="n">
         <v>24859.94636483739</v>
@@ -2238,13 +2238,13 @@
         <v>43528.95209787157</v>
       </c>
       <c r="P28" t="n">
-        <v>40273.43346841528</v>
+        <v>40273.43346841526</v>
       </c>
       <c r="Q28" t="n">
-        <v>39596.30640726308</v>
+        <v>39596.3064072631</v>
       </c>
       <c r="R28" t="n">
-        <v>46447.2040441729</v>
+        <v>46447.20404417293</v>
       </c>
       <c r="S28" t="n">
         <v>48369.35735391411</v>
@@ -2269,43 +2269,43 @@
         <v>1020011.125567459</v>
       </c>
       <c r="E29" t="n">
-        <v>1077951.19309211</v>
+        <v>1077951.193092111</v>
       </c>
       <c r="F29" t="n">
-        <v>827967.7548224226</v>
+        <v>827967.7548224229</v>
       </c>
       <c r="G29" t="n">
-        <v>965726.3493318465</v>
+        <v>965726.3493318466</v>
       </c>
       <c r="H29" t="n">
-        <v>796284.7007069287</v>
+        <v>796284.7007069293</v>
       </c>
       <c r="I29" t="n">
         <v>1147395.497650431</v>
       </c>
       <c r="J29" t="n">
-        <v>962060.6150525492</v>
+        <v>962060.6150525496</v>
       </c>
       <c r="K29" t="n">
         <v>1062442.33704377</v>
       </c>
       <c r="L29" t="n">
-        <v>1171871.425588342</v>
+        <v>1171871.425588341</v>
       </c>
       <c r="M29" t="n">
         <v>1099768.948826699</v>
       </c>
       <c r="N29" t="n">
-        <v>1197858.023697801</v>
+        <v>1197858.0236978</v>
       </c>
       <c r="O29" t="n">
         <v>1682702.54049432</v>
       </c>
       <c r="P29" t="n">
-        <v>1716233.425423574</v>
+        <v>1716233.425423573</v>
       </c>
       <c r="Q29" t="n">
-        <v>1620817.431991379</v>
+        <v>1620817.431991378</v>
       </c>
       <c r="R29" t="n">
         <v>1871441.476686289</v>
@@ -2314,7 +2314,7 @@
         <v>1971218.86050283</v>
       </c>
       <c r="T29" t="n">
-        <v>2163560.695347918</v>
+        <v>2163560.695347919</v>
       </c>
     </row>
     <row r="30">
@@ -2345,13 +2345,13 @@
         <v>1840.191746680703</v>
       </c>
       <c r="I30" t="n">
-        <v>2141.615702041054</v>
+        <v>2141.615702041053</v>
       </c>
       <c r="J30" t="n">
         <v>2058.190345260888</v>
       </c>
       <c r="K30" t="n">
-        <v>1693.639656098346</v>
+        <v>1693.639656098347</v>
       </c>
       <c r="L30" t="n">
         <v>1846.072181335701</v>
@@ -2412,10 +2412,10 @@
         <v>229.265006285289</v>
       </c>
       <c r="J31" t="n">
-        <v>203.3900880550895</v>
+        <v>203.3900880550894</v>
       </c>
       <c r="K31" t="n">
-        <v>215.2147139767864</v>
+        <v>215.2147139767863</v>
       </c>
       <c r="L31" t="n">
         <v>228.4636183230356</v>
@@ -2427,7 +2427,7 @@
         <v>254.4710004686207</v>
       </c>
       <c r="O31" t="n">
-        <v>370.6396795559247</v>
+        <v>370.6396795559248</v>
       </c>
       <c r="P31" t="n">
         <v>393.1761455553488</v>
@@ -2436,7 +2436,7 @@
         <v>335.905628601906</v>
       </c>
       <c r="R31" t="n">
-        <v>433.417343060267</v>
+        <v>433.4173430602669</v>
       </c>
       <c r="S31" t="n">
         <v>351.6370503091605</v>
@@ -2476,10 +2476,10 @@
         <v>1607700.552173858</v>
       </c>
       <c r="J32" t="n">
-        <v>1375002.870820075</v>
+        <v>1375002.870820076</v>
       </c>
       <c r="K32" t="n">
-        <v>1435387.914733986</v>
+        <v>1435387.914733985</v>
       </c>
       <c r="L32" t="n">
         <v>1693897.355388771</v>
@@ -2491,10 +2491,10 @@
         <v>1588847.584389567</v>
       </c>
       <c r="O32" t="n">
-        <v>3397043.919092382</v>
+        <v>3397043.919092381</v>
       </c>
       <c r="P32" t="n">
-        <v>3177424.521050664</v>
+        <v>3177424.521050665</v>
       </c>
       <c r="Q32" t="n">
         <v>3130345.40335029</v>
@@ -2503,10 +2503,10 @@
         <v>4814119.891852618</v>
       </c>
       <c r="S32" t="n">
-        <v>4952669.445230626</v>
+        <v>4952669.445230629</v>
       </c>
       <c r="T32" t="n">
-        <v>4734084.074709983</v>
+        <v>4734084.074709981</v>
       </c>
     </row>
     <row r="33">
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2081505.468864392</v>
+        <v>2081505.468864393</v>
       </c>
       <c r="D33" t="n">
-        <v>1847171.860583378</v>
+        <v>1847171.860583377</v>
       </c>
       <c r="E33" t="n">
-        <v>2340008.448542932</v>
+        <v>2340008.448542931</v>
       </c>
       <c r="F33" t="n">
         <v>1991635.335489462</v>
@@ -2534,43 +2534,43 @@
         <v>2065961.469128686</v>
       </c>
       <c r="H33" t="n">
-        <v>2432933.643809362</v>
+        <v>2432933.643809361</v>
       </c>
       <c r="I33" t="n">
         <v>2735097.706757521</v>
       </c>
       <c r="J33" t="n">
-        <v>2579479.946431634</v>
+        <v>2579479.946431633</v>
       </c>
       <c r="K33" t="n">
-        <v>2398575.641659608</v>
+        <v>2398575.641659607</v>
       </c>
       <c r="L33" t="n">
-        <v>2198640.920042904</v>
+        <v>2198640.920042905</v>
       </c>
       <c r="M33" t="n">
-        <v>2302572.45192345</v>
+        <v>2302572.451923451</v>
       </c>
       <c r="N33" t="n">
-        <v>2760636.257610245</v>
+        <v>2760636.257610244</v>
       </c>
       <c r="O33" t="n">
-        <v>4108614.531694909</v>
+        <v>4108614.53169491</v>
       </c>
       <c r="P33" t="n">
-        <v>4279350.681070849</v>
+        <v>4279350.681070847</v>
       </c>
       <c r="Q33" t="n">
-        <v>3663359.876602686</v>
+        <v>3663359.876602687</v>
       </c>
       <c r="R33" t="n">
-        <v>4449608.870463716</v>
+        <v>4449608.870463715</v>
       </c>
       <c r="S33" t="n">
         <v>4426034.698651074</v>
       </c>
       <c r="T33" t="n">
-        <v>4579000.165850751</v>
+        <v>4579000.16585075</v>
       </c>
     </row>
     <row r="34">
@@ -2583,13 +2583,13 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>41187.19450783979</v>
+        <v>41187.19450783978</v>
       </c>
       <c r="D34" t="n">
-        <v>34534.15084004816</v>
+        <v>34534.15084004815</v>
       </c>
       <c r="E34" t="n">
-        <v>34431.09250778696</v>
+        <v>34431.09250778695</v>
       </c>
       <c r="F34" t="n">
         <v>30431.90309797047</v>
@@ -2601,19 +2601,19 @@
         <v>43728.29234603429</v>
       </c>
       <c r="I34" t="n">
-        <v>61368.28128003459</v>
+        <v>61368.28128003457</v>
       </c>
       <c r="J34" t="n">
         <v>52585.43928913676</v>
       </c>
       <c r="K34" t="n">
-        <v>51308.12518874498</v>
+        <v>51308.12518874496</v>
       </c>
       <c r="L34" t="n">
-        <v>57981.08491742561</v>
+        <v>57981.08491742559</v>
       </c>
       <c r="M34" t="n">
-        <v>54935.73755538702</v>
+        <v>54935.73755538703</v>
       </c>
       <c r="N34" t="n">
         <v>51329.23134909572</v>
@@ -2622,7 +2622,7 @@
         <v>102973.765624694</v>
       </c>
       <c r="P34" t="n">
-        <v>97233.80972769979</v>
+        <v>97233.8097276998</v>
       </c>
       <c r="Q34" t="n">
         <v>84048.835192124</v>
@@ -2659,7 +2659,7 @@
         <v>32421.18247446101</v>
       </c>
       <c r="G35" t="n">
-        <v>32677.79805552946</v>
+        <v>32677.79805552945</v>
       </c>
       <c r="H35" t="n">
         <v>50286.69882809532</v>
@@ -2668,13 +2668,13 @@
         <v>61522.46298230164</v>
       </c>
       <c r="J35" t="n">
-        <v>49195.4274629248</v>
+        <v>49195.42746292481</v>
       </c>
       <c r="K35" t="n">
-        <v>51589.14491577139</v>
+        <v>51589.1449157714</v>
       </c>
       <c r="L35" t="n">
-        <v>57288.46630766591</v>
+        <v>57288.46630766592</v>
       </c>
       <c r="M35" t="n">
         <v>54002.89852125484</v>
@@ -2695,7 +2695,7 @@
         <v>111748.940409053</v>
       </c>
       <c r="S35" t="n">
-        <v>132384.2817429061</v>
+        <v>132384.2817429062</v>
       </c>
       <c r="T35" t="n">
         <v>131387.632509582</v>
@@ -2711,22 +2711,22 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>90385.98156312293</v>
+        <v>90385.98156312291</v>
       </c>
       <c r="D36" t="n">
-        <v>80995.73986008228</v>
+        <v>80995.73986008231</v>
       </c>
       <c r="E36" t="n">
-        <v>83311.54765040391</v>
+        <v>83311.5476504039</v>
       </c>
       <c r="F36" t="n">
         <v>77830.90380053487</v>
       </c>
       <c r="G36" t="n">
-        <v>78648.8564050976</v>
+        <v>78648.85640509763</v>
       </c>
       <c r="H36" t="n">
-        <v>65804.81943591367</v>
+        <v>65804.8194359137</v>
       </c>
       <c r="I36" t="n">
         <v>118205.7079282702</v>
@@ -2778,28 +2778,28 @@
         <v>403841.1850051032</v>
       </c>
       <c r="D37" t="n">
-        <v>332986.2332805056</v>
+        <v>332986.2332805057</v>
       </c>
       <c r="E37" t="n">
         <v>382921.9350079327</v>
       </c>
       <c r="F37" t="n">
-        <v>312500.1954636671</v>
+        <v>312500.195463667</v>
       </c>
       <c r="G37" t="n">
         <v>335857.732802933</v>
       </c>
       <c r="H37" t="n">
-        <v>494616.0264466846</v>
+        <v>494616.0264466844</v>
       </c>
       <c r="I37" t="n">
-        <v>564531.4875817858</v>
+        <v>564531.4875817859</v>
       </c>
       <c r="J37" t="n">
-        <v>495006.2278987932</v>
+        <v>495006.2278987931</v>
       </c>
       <c r="K37" t="n">
-        <v>510937.7099490456</v>
+        <v>510937.7099490455</v>
       </c>
       <c r="L37" t="n">
         <v>575795.25249221</v>
@@ -2808,13 +2808,13 @@
         <v>552973.3473931231</v>
       </c>
       <c r="N37" t="n">
-        <v>554359.4922109877</v>
+        <v>554359.4922109878</v>
       </c>
       <c r="O37" t="n">
         <v>858902.2450419985</v>
       </c>
       <c r="P37" t="n">
-        <v>888979.1471005252</v>
+        <v>888979.1471005254</v>
       </c>
       <c r="Q37" t="n">
         <v>806016.2953737392</v>
@@ -2863,13 +2863,13 @@
         <v>14437.88983608917</v>
       </c>
       <c r="K38" t="n">
-        <v>14677.02997721677</v>
+        <v>14677.02997721676</v>
       </c>
       <c r="L38" t="n">
         <v>17916.19580757056</v>
       </c>
       <c r="M38" t="n">
-        <v>17192.8549130847</v>
+        <v>17192.85491308471</v>
       </c>
       <c r="N38" t="n">
         <v>17513.86923542408</v>
@@ -2884,7 +2884,7 @@
         <v>29303.62551746471</v>
       </c>
       <c r="R38" t="n">
-        <v>34715.09298488562</v>
+        <v>34715.09298488563</v>
       </c>
       <c r="S38" t="n">
         <v>34541.28326010521</v>
@@ -2906,7 +2906,7 @@
         <v>7971.44616065694</v>
       </c>
       <c r="D39" t="n">
-        <v>7938.856005095247</v>
+        <v>7938.856005095248</v>
       </c>
       <c r="E39" t="n">
         <v>8868.895793980246</v>
@@ -2921,7 +2921,7 @@
         <v>6706.694821649803</v>
       </c>
       <c r="I39" t="n">
-        <v>9733.879464700896</v>
+        <v>9733.879464700898</v>
       </c>
       <c r="J39" t="n">
         <v>8003.633001835672</v>
@@ -2930,7 +2930,7 @@
         <v>8010.526985455528</v>
       </c>
       <c r="L39" t="n">
-        <v>9787.784878835115</v>
+        <v>9787.784878835113</v>
       </c>
       <c r="M39" t="n">
         <v>9327.848581455393</v>
@@ -2970,7 +2970,7 @@
         <v>4080.46965243525</v>
       </c>
       <c r="D40" t="n">
-        <v>3033.286693929381</v>
+        <v>3033.28669392938</v>
       </c>
       <c r="E40" t="n">
         <v>3344.863286956429</v>
@@ -2985,7 +2985,7 @@
         <v>3890.403332600476</v>
       </c>
       <c r="I40" t="n">
-        <v>5285.010112432355</v>
+        <v>5285.010112432356</v>
       </c>
       <c r="J40" t="n">
         <v>4551.752643467245</v>
@@ -2994,22 +2994,22 @@
         <v>4310.855393362268</v>
       </c>
       <c r="L40" t="n">
-        <v>5329.588401387921</v>
+        <v>5329.588401387922</v>
       </c>
       <c r="M40" t="n">
         <v>4932.372826955176</v>
       </c>
       <c r="N40" t="n">
-        <v>5062.096089129985</v>
+        <v>5062.096089129986</v>
       </c>
       <c r="O40" t="n">
-        <v>8161.055578085139</v>
+        <v>8161.055578085138</v>
       </c>
       <c r="P40" t="n">
-        <v>8140.907308561286</v>
+        <v>8140.907308561285</v>
       </c>
       <c r="Q40" t="n">
-        <v>9103.510646740868</v>
+        <v>9103.510646740866</v>
       </c>
       <c r="R40" t="n">
         <v>11487.43491367986</v>
@@ -3037,13 +3037,13 @@
         <v>9134.872175990984</v>
       </c>
       <c r="E41" t="n">
-        <v>9872.828362054066</v>
+        <v>9872.828362054064</v>
       </c>
       <c r="F41" t="n">
         <v>9193.92198909579</v>
       </c>
       <c r="G41" t="n">
-        <v>9532.254180683803</v>
+        <v>9532.254180683802</v>
       </c>
       <c r="H41" t="n">
         <v>19380.32014399327</v>
@@ -3058,13 +3058,13 @@
         <v>12060.32388488669</v>
       </c>
       <c r="L41" t="n">
-        <v>19681.80918572986</v>
+        <v>19681.80918572985</v>
       </c>
       <c r="M41" t="n">
         <v>14073.7164498462</v>
       </c>
       <c r="N41" t="n">
-        <v>13519.35784148156</v>
+        <v>13519.35784148155</v>
       </c>
       <c r="O41" t="n">
         <v>23572.60771273787</v>
@@ -3082,7 +3082,7 @@
         <v>26491.5048997362</v>
       </c>
       <c r="T41" t="n">
-        <v>27738.80019230579</v>
+        <v>27738.80019230578</v>
       </c>
     </row>
     <row r="42">
@@ -3104,7 +3104,7 @@
         <v>23552.04483189218</v>
       </c>
       <c r="F42" t="n">
-        <v>20598.00953303267</v>
+        <v>20598.00953303266</v>
       </c>
       <c r="G42" t="n">
         <v>22068.84047898258</v>
@@ -3113,7 +3113,7 @@
         <v>25756.53979779442</v>
       </c>
       <c r="I42" t="n">
-        <v>30414.24558382796</v>
+        <v>30414.24558382797</v>
       </c>
       <c r="J42" t="n">
         <v>24962.64871038972</v>
@@ -3134,7 +3134,7 @@
         <v>40015.93447106327</v>
       </c>
       <c r="P42" t="n">
-        <v>41576.81114821924</v>
+        <v>41576.81114821925</v>
       </c>
       <c r="Q42" t="n">
         <v>44925.65187712045</v>
@@ -3146,7 +3146,7 @@
         <v>52105.57963078457</v>
       </c>
       <c r="T42" t="n">
-        <v>49540.19897584025</v>
+        <v>49540.19897584024</v>
       </c>
     </row>
     <row r="43">
@@ -3159,7 +3159,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>37627.62177254188</v>
+        <v>37627.62177254187</v>
       </c>
       <c r="D43" t="n">
         <v>31058.50856688692</v>
@@ -3168,31 +3168,31 @@
         <v>36263.30037252947</v>
       </c>
       <c r="F43" t="n">
-        <v>31240.59637749165</v>
+        <v>31240.59637749164</v>
       </c>
       <c r="G43" t="n">
         <v>35980.03405057047</v>
       </c>
       <c r="H43" t="n">
-        <v>59814.21278495598</v>
+        <v>59814.21278495599</v>
       </c>
       <c r="I43" t="n">
-        <v>64642.83152723199</v>
+        <v>64642.83152723198</v>
       </c>
       <c r="J43" t="n">
-        <v>49916.24891881441</v>
+        <v>49916.24891881442</v>
       </c>
       <c r="K43" t="n">
-        <v>59689.19565359035</v>
+        <v>59689.19565359036</v>
       </c>
       <c r="L43" t="n">
-        <v>68524.34087814586</v>
+        <v>68524.34087814587</v>
       </c>
       <c r="M43" t="n">
-        <v>64086.14287886241</v>
+        <v>64086.14287886239</v>
       </c>
       <c r="N43" t="n">
-        <v>64634.1885904472</v>
+        <v>64634.18859044721</v>
       </c>
       <c r="O43" t="n">
         <v>132548.0102311597</v>
@@ -3201,16 +3201,16 @@
         <v>131455.8575236182</v>
       </c>
       <c r="Q43" t="n">
-        <v>138589.7227139588</v>
+        <v>138589.7227139589</v>
       </c>
       <c r="R43" t="n">
-        <v>135421.7567644904</v>
+        <v>135421.7567644905</v>
       </c>
       <c r="S43" t="n">
         <v>165921.3610414616</v>
       </c>
       <c r="T43" t="n">
-        <v>182242.1787242287</v>
+        <v>182242.1787242286</v>
       </c>
     </row>
     <row r="44">
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>267993.628356013</v>
+        <v>267993.6283560131</v>
       </c>
       <c r="D44" t="n">
         <v>227093.8473575154</v>
@@ -3232,10 +3232,10 @@
         <v>209162.1938027627</v>
       </c>
       <c r="F44" t="n">
-        <v>210165.4827249329</v>
+        <v>210165.4827249328</v>
       </c>
       <c r="G44" t="n">
-        <v>229602.096486812</v>
+        <v>229602.0964868119</v>
       </c>
       <c r="H44" t="n">
         <v>241997.6787438558</v>
@@ -3247,34 +3247,34 @@
         <v>310660.4857656152</v>
       </c>
       <c r="K44" t="n">
-        <v>319461.4298235964</v>
+        <v>319461.4298235963</v>
       </c>
       <c r="L44" t="n">
-        <v>373704.9932564594</v>
+        <v>373704.9932564593</v>
       </c>
       <c r="M44" t="n">
-        <v>348927.8556313221</v>
+        <v>348927.855631322</v>
       </c>
       <c r="N44" t="n">
-        <v>359439.0440914878</v>
+        <v>359439.0440914877</v>
       </c>
       <c r="O44" t="n">
         <v>668188.4178368183</v>
       </c>
       <c r="P44" t="n">
-        <v>707934.6432801986</v>
+        <v>707934.6432801987</v>
       </c>
       <c r="Q44" t="n">
-        <v>687325.9240134584</v>
+        <v>687325.9240134587</v>
       </c>
       <c r="R44" t="n">
-        <v>793122.0564760473</v>
+        <v>793122.0564760475</v>
       </c>
       <c r="S44" t="n">
         <v>902737.2369003957</v>
       </c>
       <c r="T44" t="n">
-        <v>932839.1079496909</v>
+        <v>932839.1079496911</v>
       </c>
     </row>
     <row r="45">
@@ -3299,7 +3299,7 @@
         <v>5237.438556591888</v>
       </c>
       <c r="G45" t="n">
-        <v>5111.08876892459</v>
+        <v>5111.088768924589</v>
       </c>
       <c r="H45" t="n">
         <v>5076.194376675767</v>
@@ -3311,7 +3311,7 @@
         <v>7667.080448923318</v>
       </c>
       <c r="K45" t="n">
-        <v>8617.76175149703</v>
+        <v>8617.761751497032</v>
       </c>
       <c r="L45" t="n">
         <v>9954.579770019645</v>
@@ -3338,7 +3338,7 @@
         <v>31728.52002819892</v>
       </c>
       <c r="T45" t="n">
-        <v>30123.76374782035</v>
+        <v>30123.76374782036</v>
       </c>
     </row>
     <row r="46">
@@ -3399,10 +3399,10 @@
         <v>3113.861513964946</v>
       </c>
       <c r="S46" t="n">
-        <v>3009.201252960765</v>
+        <v>3009.201252960764</v>
       </c>
       <c r="T46" t="n">
-        <v>3676.447344176928</v>
+        <v>3676.447344176927</v>
       </c>
     </row>
     <row r="47">
@@ -3415,13 +3415,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>7131.672076925497</v>
+        <v>7131.672076925498</v>
       </c>
       <c r="D47" t="n">
-        <v>8256.780768894616</v>
+        <v>8256.780768894618</v>
       </c>
       <c r="E47" t="n">
-        <v>6369.115188915137</v>
+        <v>6369.115188915136</v>
       </c>
       <c r="F47" t="n">
         <v>5910.776639389867</v>
@@ -3439,16 +3439,16 @@
         <v>7266.695844755671</v>
       </c>
       <c r="K47" t="n">
-        <v>6315.25211750797</v>
+        <v>6315.252117507971</v>
       </c>
       <c r="L47" t="n">
         <v>8514.014139237965</v>
       </c>
       <c r="M47" t="n">
-        <v>8194.286992326202</v>
+        <v>8194.286992326201</v>
       </c>
       <c r="N47" t="n">
-        <v>8817.136456389804</v>
+        <v>8817.136456389806</v>
       </c>
       <c r="O47" t="n">
         <v>12102.26844103483</v>
@@ -3488,7 +3488,7 @@
         <v>115879.8934665405</v>
       </c>
       <c r="F48" t="n">
-        <v>87394.46598113602</v>
+        <v>87394.465981136</v>
       </c>
       <c r="G48" t="n">
         <v>113889.4155687358</v>
@@ -3515,22 +3515,22 @@
         <v>157904.3516290819</v>
       </c>
       <c r="O48" t="n">
-        <v>298069.5793343357</v>
+        <v>298069.5793343358</v>
       </c>
       <c r="P48" t="n">
         <v>314575.9366060627</v>
       </c>
       <c r="Q48" t="n">
-        <v>269487.5652407509</v>
+        <v>269487.565240751</v>
       </c>
       <c r="R48" t="n">
-        <v>378983.9943300821</v>
+        <v>378983.994330082</v>
       </c>
       <c r="S48" t="n">
         <v>502662.4507006324</v>
       </c>
       <c r="T48" t="n">
-        <v>483678.4257655766</v>
+        <v>483678.4257655767</v>
       </c>
     </row>
     <row r="49">
@@ -3607,22 +3607,22 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5013.934126533647</v>
+        <v>5013.934126533646</v>
       </c>
       <c r="D50" t="n">
-        <v>4139.667321161483</v>
+        <v>4139.667321161482</v>
       </c>
       <c r="E50" t="n">
         <v>4807.177733421498</v>
       </c>
       <c r="F50" t="n">
-        <v>3913.707410217265</v>
+        <v>3913.707410217266</v>
       </c>
       <c r="G50" t="n">
         <v>3869.897247942421</v>
       </c>
       <c r="H50" t="n">
-        <v>5656.874727430524</v>
+        <v>5656.874727430526</v>
       </c>
       <c r="I50" t="n">
         <v>6544.169408739275</v>
@@ -3637,7 +3637,7 @@
         <v>7321.599448643567</v>
       </c>
       <c r="M50" t="n">
-        <v>7443.518925194218</v>
+        <v>7443.518925194217</v>
       </c>
       <c r="N50" t="n">
         <v>6661.645505494893</v>
@@ -3652,13 +3652,13 @@
         <v>14991.60832653223</v>
       </c>
       <c r="R50" t="n">
-        <v>18670.99622671242</v>
+        <v>18670.99622671243</v>
       </c>
       <c r="S50" t="n">
         <v>20909.98564114795</v>
       </c>
       <c r="T50" t="n">
-        <v>18853.06206798266</v>
+        <v>18853.06206798267</v>
       </c>
     </row>
     <row r="51">
@@ -3704,25 +3704,25 @@
         <v>1946536.528898072</v>
       </c>
       <c r="N51" t="n">
-        <v>1832204.412791071</v>
+        <v>1832204.41279107</v>
       </c>
       <c r="O51" t="n">
-        <v>4800994.74170795</v>
+        <v>4800994.741707948</v>
       </c>
       <c r="P51" t="n">
-        <v>4802777.221144307</v>
+        <v>4802777.221144308</v>
       </c>
       <c r="Q51" t="n">
-        <v>4826997.780332588</v>
+        <v>4826997.780332589</v>
       </c>
       <c r="R51" t="n">
-        <v>7434461.153010927</v>
+        <v>7434461.153010925</v>
       </c>
       <c r="S51" t="n">
-        <v>8076031.857965281</v>
+        <v>8076031.857965284</v>
       </c>
       <c r="T51" t="n">
-        <v>7605595.177754575</v>
+        <v>7605595.177754574</v>
       </c>
     </row>
     <row r="52">
@@ -3741,7 +3741,7 @@
         <v>9537.916063363718</v>
       </c>
       <c r="E52" t="n">
-        <v>9255.385105254849</v>
+        <v>9255.385105254847</v>
       </c>
       <c r="F52" t="n">
         <v>9464.414806152025</v>
@@ -3753,7 +3753,7 @@
         <v>12333.98638246758</v>
       </c>
       <c r="I52" t="n">
-        <v>16860.74609392448</v>
+        <v>16860.74609392447</v>
       </c>
       <c r="J52" t="n">
         <v>14450.4445926258</v>
@@ -3762,7 +3762,7 @@
         <v>14883.60551104985</v>
       </c>
       <c r="L52" t="n">
-        <v>17110.49924815764</v>
+        <v>17110.49924815765</v>
       </c>
       <c r="M52" t="n">
         <v>16852.95946033864</v>
@@ -3771,16 +3771,16 @@
         <v>17576.21298283095</v>
       </c>
       <c r="O52" t="n">
-        <v>27463.54527525754</v>
+        <v>27463.54527525753</v>
       </c>
       <c r="P52" t="n">
-        <v>27316.03982735389</v>
+        <v>27316.0398273539</v>
       </c>
       <c r="Q52" t="n">
-        <v>24663.90861521309</v>
+        <v>24663.9086152131</v>
       </c>
       <c r="R52" t="n">
-        <v>28536.201573749</v>
+        <v>28536.20157374899</v>
       </c>
       <c r="S52" t="n">
         <v>29415.3189689198</v>
@@ -3799,13 +3799,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2795.706630616396</v>
+        <v>2795.706630616397</v>
       </c>
       <c r="D53" t="n">
         <v>2726.099113629045</v>
       </c>
       <c r="E53" t="n">
-        <v>2669.358334557922</v>
+        <v>2669.358334557921</v>
       </c>
       <c r="F53" t="n">
         <v>2216.646076544006</v>
@@ -3820,7 +3820,7 @@
         <v>2965.260855735509</v>
       </c>
       <c r="J53" t="n">
-        <v>2444.948465548793</v>
+        <v>2444.948465548792</v>
       </c>
       <c r="K53" t="n">
         <v>2596.737045035115</v>
@@ -3835,16 +3835,16 @@
         <v>3052.584563690922</v>
       </c>
       <c r="O53" t="n">
-        <v>4278.62525831553</v>
+        <v>4278.625258315529</v>
       </c>
       <c r="P53" t="n">
-        <v>4707.788228928455</v>
+        <v>4707.788228928454</v>
       </c>
       <c r="Q53" t="n">
         <v>4082.567723420402</v>
       </c>
       <c r="R53" t="n">
-        <v>4635.332365372449</v>
+        <v>4635.33236537245</v>
       </c>
       <c r="S53" t="n">
         <v>4585.516286426608</v>
@@ -3869,7 +3869,7 @@
         <v>1385110.656603</v>
       </c>
       <c r="E54" t="n">
-        <v>1555163.3880197</v>
+        <v>1555163.388019701</v>
       </c>
       <c r="F54" t="n">
         <v>1072214.001990369</v>
@@ -3878,10 +3878,10 @@
         <v>1318513.196452609</v>
       </c>
       <c r="H54" t="n">
-        <v>1321165.722485675</v>
+        <v>1321165.722485676</v>
       </c>
       <c r="I54" t="n">
-        <v>1802399.570532564</v>
+        <v>1802399.570532563</v>
       </c>
       <c r="J54" t="n">
         <v>1494734.474853311</v>
@@ -3899,10 +3899,10 @@
         <v>1800254.359802373</v>
       </c>
       <c r="O54" t="n">
-        <v>4581324.967122583</v>
+        <v>4581324.967122582</v>
       </c>
       <c r="P54" t="n">
-        <v>3890544.846823702</v>
+        <v>3890544.846823703</v>
       </c>
       <c r="Q54" t="n">
         <v>3865055.089389981</v>
@@ -3911,10 +3911,10 @@
         <v>5653782.90547652</v>
       </c>
       <c r="S54" t="n">
-        <v>6390479.297575319</v>
+        <v>6390479.297575316</v>
       </c>
       <c r="T54" t="n">
-        <v>6298267.966389866</v>
+        <v>6298267.966389865</v>
       </c>
     </row>
     <row r="55">
@@ -3927,7 +3927,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>122685.5596883034</v>
+        <v>122685.5596883035</v>
       </c>
       <c r="D55" t="n">
         <v>104281.8170986645</v>
@@ -3942,19 +3942,19 @@
         <v>116047.7471717044</v>
       </c>
       <c r="H55" t="n">
-        <v>154835.3840703868</v>
+        <v>154835.3840703869</v>
       </c>
       <c r="I55" t="n">
         <v>171348.2952806354</v>
       </c>
       <c r="J55" t="n">
-        <v>143573.6931952264</v>
+        <v>143573.6931952265</v>
       </c>
       <c r="K55" t="n">
-        <v>154437.5027569812</v>
+        <v>154437.5027569813</v>
       </c>
       <c r="L55" t="n">
-        <v>168223.2498827324</v>
+        <v>168223.2498827323</v>
       </c>
       <c r="M55" t="n">
         <v>158199.8510386045</v>
@@ -3966,10 +3966,10 @@
         <v>273231.9878236793</v>
       </c>
       <c r="P55" t="n">
-        <v>257279.930617304</v>
+        <v>257279.9306173041</v>
       </c>
       <c r="Q55" t="n">
-        <v>257909.2278840739</v>
+        <v>257909.227884074</v>
       </c>
       <c r="R55" t="n">
         <v>306274.7485541186</v>
@@ -3978,7 +3978,7 @@
         <v>342525.4159981149</v>
       </c>
       <c r="T55" t="n">
-        <v>325529.798072024</v>
+        <v>325529.7980720241</v>
       </c>
     </row>
     <row r="56">
@@ -3991,25 +3991,25 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>671892.8432882112</v>
+        <v>671892.8432882114</v>
       </c>
       <c r="D56" t="n">
-        <v>595415.941279572</v>
+        <v>595415.9412795721</v>
       </c>
       <c r="E56" t="n">
-        <v>619434.4673939077</v>
+        <v>619434.4673939078</v>
       </c>
       <c r="F56" t="n">
-        <v>706221.5074598193</v>
+        <v>706221.5074598192</v>
       </c>
       <c r="G56" t="n">
-        <v>737855.3330717026</v>
+        <v>737855.3330717025</v>
       </c>
       <c r="H56" t="n">
-        <v>747214.6830657842</v>
+        <v>747214.683065784</v>
       </c>
       <c r="I56" t="n">
-        <v>1199902.702483414</v>
+        <v>1199902.702483415</v>
       </c>
       <c r="J56" t="n">
         <v>1013755.243384423</v>
@@ -4024,7 +4024,7 @@
         <v>1255217.871322888</v>
       </c>
       <c r="N56" t="n">
-        <v>1342582.767783154</v>
+        <v>1342582.767783153</v>
       </c>
       <c r="O56" t="n">
         <v>2080951.928264528</v>
@@ -4042,7 +4042,7 @@
         <v>2268317.873198081</v>
       </c>
       <c r="T56" t="n">
-        <v>2481832.90998939</v>
+        <v>2481832.909989389</v>
       </c>
     </row>
     <row r="57">
@@ -4058,7 +4058,7 @@
         <v>10114.40195912405</v>
       </c>
       <c r="D57" t="n">
-        <v>8896.730362645318</v>
+        <v>8896.730362645316</v>
       </c>
       <c r="E57" t="n">
         <v>11092.45965813669</v>
@@ -4128,10 +4128,10 @@
         <v>19110.61795572406</v>
       </c>
       <c r="F58" t="n">
-        <v>18300.38210318897</v>
+        <v>18300.38210318896</v>
       </c>
       <c r="G58" t="n">
-        <v>20070.49046387719</v>
+        <v>20070.4904638772</v>
       </c>
       <c r="H58" t="n">
         <v>13692.07424991724</v>
@@ -4140,7 +4140,7 @@
         <v>25091.83072569139</v>
       </c>
       <c r="J58" t="n">
-        <v>20518.10336850259</v>
+        <v>20518.10336850258</v>
       </c>
       <c r="K58" t="n">
         <v>21658.94448018866</v>
@@ -4158,19 +4158,19 @@
         <v>37800.2396433441</v>
       </c>
       <c r="P58" t="n">
-        <v>36986.54203990628</v>
+        <v>36986.54203990629</v>
       </c>
       <c r="Q58" t="n">
-        <v>38288.59653400583</v>
+        <v>38288.59653400584</v>
       </c>
       <c r="R58" t="n">
-        <v>39967.78498574585</v>
+        <v>39967.78498574584</v>
       </c>
       <c r="S58" t="n">
         <v>43812.67371504894</v>
       </c>
       <c r="T58" t="n">
-        <v>44432.67961890335</v>
+        <v>44432.67961890336</v>
       </c>
     </row>
     <row r="59">
@@ -4210,7 +4210,7 @@
         <v>25249.09955390902</v>
       </c>
       <c r="L59" t="n">
-        <v>29235.12310836633</v>
+        <v>29235.12310836634</v>
       </c>
       <c r="M59" t="n">
         <v>29300.04411746852</v>
@@ -4219,13 +4219,13 @@
         <v>28200.26043049916</v>
       </c>
       <c r="O59" t="n">
-        <v>45485.70683084932</v>
+        <v>45485.70683084933</v>
       </c>
       <c r="P59" t="n">
-        <v>47270.67959837238</v>
+        <v>47270.6795983724</v>
       </c>
       <c r="Q59" t="n">
-        <v>44341.24179903626</v>
+        <v>44341.24179903625</v>
       </c>
       <c r="R59" t="n">
         <v>59601.41010080201</v>
@@ -4234,7 +4234,7 @@
         <v>49676.17407666067</v>
       </c>
       <c r="T59" t="n">
-        <v>55855.57282392973</v>
+        <v>55855.57282392974</v>
       </c>
     </row>
     <row r="60">
@@ -4250,16 +4250,16 @@
         <v>181926.9054440719</v>
       </c>
       <c r="D60" t="n">
-        <v>161932.0432769029</v>
+        <v>161932.043276903</v>
       </c>
       <c r="E60" t="n">
-        <v>182595.4313839754</v>
+        <v>182595.4313839755</v>
       </c>
       <c r="F60" t="n">
-        <v>201238.2831360556</v>
+        <v>201238.2831360555</v>
       </c>
       <c r="G60" t="n">
-        <v>197554.0280719639</v>
+        <v>197554.0280719638</v>
       </c>
       <c r="H60" t="n">
         <v>236576.2887335363</v>
@@ -4268,19 +4268,19 @@
         <v>327516.0639216629</v>
       </c>
       <c r="J60" t="n">
-        <v>286427.9965876181</v>
+        <v>286427.9965876182</v>
       </c>
       <c r="K60" t="n">
         <v>287901.0554295115</v>
       </c>
       <c r="L60" t="n">
-        <v>332200.2154411116</v>
+        <v>332200.2154411117</v>
       </c>
       <c r="M60" t="n">
         <v>321020.1072478801</v>
       </c>
       <c r="N60" t="n">
-        <v>347779.0771617735</v>
+        <v>347779.0771617734</v>
       </c>
       <c r="O60" t="n">
         <v>498621.2845173963</v>
@@ -4292,10 +4292,10 @@
         <v>506288.6040424887</v>
       </c>
       <c r="R60" t="n">
-        <v>586210.7945868615</v>
+        <v>586210.7945868617</v>
       </c>
       <c r="S60" t="n">
-        <v>604334.1439941433</v>
+        <v>604334.1439941435</v>
       </c>
       <c r="T60" t="n">
         <v>634666.594214874</v>
@@ -4311,13 +4311,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>12817.60659380326</v>
+        <v>12817.60659380327</v>
       </c>
       <c r="D61" t="n">
         <v>12589.57048811611</v>
       </c>
       <c r="E61" t="n">
-        <v>9890.274758276544</v>
+        <v>9890.274758276546</v>
       </c>
       <c r="F61" t="n">
         <v>10364.27915039507</v>
@@ -4329,16 +4329,16 @@
         <v>14992.79598319852</v>
       </c>
       <c r="I61" t="n">
-        <v>18613.2076699283</v>
+        <v>18613.20766992829</v>
       </c>
       <c r="J61" t="n">
-        <v>16172.79716051219</v>
+        <v>16172.7971605122</v>
       </c>
       <c r="K61" t="n">
         <v>14657.39011134291</v>
       </c>
       <c r="L61" t="n">
-        <v>17012.9023031466</v>
+        <v>17012.90230314661</v>
       </c>
       <c r="M61" t="n">
         <v>16553.08612069665</v>
@@ -4347,19 +4347,19 @@
         <v>16484.65854036658</v>
       </c>
       <c r="O61" t="n">
-        <v>26718.02105139748</v>
+        <v>26718.02105139747</v>
       </c>
       <c r="P61" t="n">
-        <v>30418.40708902746</v>
+        <v>30418.40708902745</v>
       </c>
       <c r="Q61" t="n">
-        <v>30773.11870204185</v>
+        <v>30773.11870204186</v>
       </c>
       <c r="R61" t="n">
         <v>41581.664801306</v>
       </c>
       <c r="S61" t="n">
-        <v>45383.46984030756</v>
+        <v>45383.46984030757</v>
       </c>
       <c r="T61" t="n">
         <v>39477.98255272324</v>
@@ -4411,7 +4411,7 @@
         <v>4559.332484158752</v>
       </c>
       <c r="O62" t="n">
-        <v>323.3517106689234</v>
+        <v>323.3517106689235</v>
       </c>
       <c r="P62" t="n">
         <v>3567.963838670462</v>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>369667.9928633039</v>
+        <v>369667.9928633038</v>
       </c>
       <c r="D63" t="n">
         <v>361032.9690159347</v>
@@ -4448,13 +4448,13 @@
         <v>377606.2730589883</v>
       </c>
       <c r="F63" t="n">
-        <v>272109.9413965411</v>
+        <v>272109.9413965412</v>
       </c>
       <c r="G63" t="n">
-        <v>333987.1225312496</v>
+        <v>333987.1225312497</v>
       </c>
       <c r="H63" t="n">
-        <v>404474.1263417601</v>
+        <v>404474.1263417602</v>
       </c>
       <c r="I63" t="n">
         <v>392852.3065003175</v>
@@ -4463,34 +4463,34 @@
         <v>363505.0187315309</v>
       </c>
       <c r="K63" t="n">
-        <v>354124.0758276526</v>
+        <v>354124.0758276527</v>
       </c>
       <c r="L63" t="n">
-        <v>323483.0587131186</v>
+        <v>323483.0587131187</v>
       </c>
       <c r="M63" t="n">
         <v>341922.0547193206</v>
       </c>
       <c r="N63" t="n">
-        <v>394087.163764359</v>
+        <v>394087.1637643591</v>
       </c>
       <c r="O63" t="n">
-        <v>416751.9860754073</v>
+        <v>416751.9860754074</v>
       </c>
       <c r="P63" t="n">
-        <v>421018.3951631029</v>
+        <v>421018.395163103</v>
       </c>
       <c r="Q63" t="n">
-        <v>360464.4282110947</v>
+        <v>360464.4282110948</v>
       </c>
       <c r="R63" t="n">
         <v>493231.0930350344</v>
       </c>
       <c r="S63" t="n">
-        <v>502737.5735577964</v>
+        <v>502737.5735577962</v>
       </c>
       <c r="T63" t="n">
-        <v>433535.7476938888</v>
+        <v>433535.7476938887</v>
       </c>
     </row>
     <row r="64">
@@ -4515,10 +4515,10 @@
         <v>1994.842201968086</v>
       </c>
       <c r="G64" t="n">
-        <v>2389.514427277149</v>
+        <v>2389.514427277148</v>
       </c>
       <c r="H64" t="n">
-        <v>2915.705867484191</v>
+        <v>2915.70586748419</v>
       </c>
       <c r="I64" t="n">
         <v>3496.789465959517</v>
@@ -4533,7 +4533,7 @@
         <v>3757.12140904561</v>
       </c>
       <c r="M64" t="n">
-        <v>3838.793558593578</v>
+        <v>3838.793558593579</v>
       </c>
       <c r="N64" t="n">
         <v>3782.983726580804</v>
@@ -4542,7 +4542,7 @@
         <v>9789.199657453135</v>
       </c>
       <c r="P64" t="n">
-        <v>9724.025114324013</v>
+        <v>9724.025114324011</v>
       </c>
       <c r="Q64" t="n">
         <v>7018.451879679068</v>
@@ -4570,13 +4570,13 @@
         <v>776350.280029088</v>
       </c>
       <c r="D65" t="n">
-        <v>740502.7269995646</v>
+        <v>740502.7269995647</v>
       </c>
       <c r="E65" t="n">
-        <v>743819.4367747777</v>
+        <v>743819.4367747778</v>
       </c>
       <c r="F65" t="n">
-        <v>420072.1505239242</v>
+        <v>420072.1505239243</v>
       </c>
       <c r="G65" t="n">
         <v>451037.9432733154</v>
@@ -4585,13 +4585,13 @@
         <v>699712.0598411903</v>
       </c>
       <c r="I65" t="n">
-        <v>680010.7903891099</v>
+        <v>680010.79038911</v>
       </c>
       <c r="J65" t="n">
         <v>589137.0375680829</v>
       </c>
       <c r="K65" t="n">
-        <v>610955.072334555</v>
+        <v>610955.0723345549</v>
       </c>
       <c r="L65" t="n">
         <v>708845.6776129021</v>
@@ -4615,10 +4615,10 @@
         <v>1488020.7872017</v>
       </c>
       <c r="S65" t="n">
-        <v>1389957.907524279</v>
+        <v>1389957.90752428</v>
       </c>
       <c r="T65" t="n">
-        <v>1523064.798809355</v>
+        <v>1523064.798809356</v>
       </c>
     </row>
     <row r="66">
@@ -4631,7 +4631,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>33545.4493213833</v>
+        <v>33545.44932138331</v>
       </c>
       <c r="D66" t="n">
         <v>28724.77998306785</v>
@@ -4646,16 +4646,16 @@
         <v>30223.84830516051</v>
       </c>
       <c r="H66" t="n">
-        <v>41301.98693122104</v>
+        <v>41301.98693122103</v>
       </c>
       <c r="I66" t="n">
         <v>51185.87865987954</v>
       </c>
       <c r="J66" t="n">
-        <v>43603.69887731687</v>
+        <v>43603.69887731686</v>
       </c>
       <c r="K66" t="n">
-        <v>43763.50823550541</v>
+        <v>43763.5082355054</v>
       </c>
       <c r="L66" t="n">
         <v>47775.54053733312</v>
@@ -4667,10 +4667,10 @@
         <v>47216.81452494478</v>
       </c>
       <c r="O66" t="n">
-        <v>84617.03340048149</v>
+        <v>84617.03340048146</v>
       </c>
       <c r="P66" t="n">
-        <v>81943.15291547723</v>
+        <v>81943.1529154772</v>
       </c>
       <c r="Q66" t="n">
         <v>85017.28557075388</v>
@@ -4682,7 +4682,7 @@
         <v>103682.130470796</v>
       </c>
       <c r="T66" t="n">
-        <v>95276.92931403065</v>
+        <v>95276.92931403067</v>
       </c>
     </row>
     <row r="67">
@@ -4698,16 +4698,16 @@
         <v>918.550078007692</v>
       </c>
       <c r="D67" t="n">
-        <v>833.1335314855719</v>
+        <v>833.1335314855718</v>
       </c>
       <c r="E67" t="n">
-        <v>787.4690255747208</v>
+        <v>787.4690255747209</v>
       </c>
       <c r="F67" t="n">
-        <v>713.5250907354063</v>
+        <v>713.5250907354061</v>
       </c>
       <c r="G67" t="n">
-        <v>757.7145391546161</v>
+        <v>757.714539154616</v>
       </c>
       <c r="H67" t="n">
         <v>728.7800129024502</v>
@@ -4722,13 +4722,13 @@
         <v>854.6759232079437</v>
       </c>
       <c r="L67" t="n">
-        <v>899.0488389692096</v>
+        <v>899.0488389692097</v>
       </c>
       <c r="M67" t="n">
-        <v>836.2940014866927</v>
+        <v>836.2940014866928</v>
       </c>
       <c r="N67" t="n">
-        <v>903.3935435932055</v>
+        <v>903.3935435932057</v>
       </c>
       <c r="O67" t="n">
         <v>1219.530613166689</v>
@@ -4743,7 +4743,7 @@
         <v>1453.880608237861</v>
       </c>
       <c r="S67" t="n">
-        <v>1340.4966673751</v>
+        <v>1340.496667375101</v>
       </c>
       <c r="T67" t="n">
         <v>1371.778439920429</v>
@@ -4759,40 +4759,40 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>5519.406142632432</v>
+        <v>5519.406142632433</v>
       </c>
       <c r="D68" t="n">
         <v>5354.119087831984</v>
       </c>
       <c r="E68" t="n">
-        <v>4972.782725771836</v>
+        <v>4972.782725771837</v>
       </c>
       <c r="F68" t="n">
-        <v>4876.458490293707</v>
+        <v>4876.458490293708</v>
       </c>
       <c r="G68" t="n">
         <v>4933.212218518223</v>
       </c>
       <c r="H68" t="n">
-        <v>5543.602187954242</v>
+        <v>5543.602187954243</v>
       </c>
       <c r="I68" t="n">
-        <v>7916.142951923664</v>
+        <v>7916.142951923665</v>
       </c>
       <c r="J68" t="n">
-        <v>6254.059507700016</v>
+        <v>6254.059507700015</v>
       </c>
       <c r="K68" t="n">
-        <v>7190.824936226874</v>
+        <v>7190.824936226873</v>
       </c>
       <c r="L68" t="n">
         <v>7826.98682678196</v>
       </c>
       <c r="M68" t="n">
-        <v>7102.795036895458</v>
+        <v>7102.795036895457</v>
       </c>
       <c r="N68" t="n">
-        <v>7659.526977316358</v>
+        <v>7659.526977316359</v>
       </c>
       <c r="O68" t="n">
         <v>13908.49406064201</v>
@@ -4829,7 +4829,7 @@
         <v>9295.582261489082</v>
       </c>
       <c r="E69" t="n">
-        <v>8364.104487214578</v>
+        <v>8364.104487214579</v>
       </c>
       <c r="F69" t="n">
         <v>9336.242861827066</v>
@@ -4838,19 +4838,19 @@
         <v>9320.657470704276</v>
       </c>
       <c r="H69" t="n">
-        <v>15030.20821328851</v>
+        <v>15030.20821328852</v>
       </c>
       <c r="I69" t="n">
         <v>18659.13372884595</v>
       </c>
       <c r="J69" t="n">
-        <v>16464.48995885719</v>
+        <v>16464.4899588572</v>
       </c>
       <c r="K69" t="n">
         <v>15356.47118683402</v>
       </c>
       <c r="L69" t="n">
-        <v>17219.59577004747</v>
+        <v>17219.59577004746</v>
       </c>
       <c r="M69" t="n">
         <v>17179.30202019528</v>
@@ -4951,7 +4951,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>628608.314528031</v>
+        <v>628608.3145280309</v>
       </c>
       <c r="D71" t="n">
         <v>625512.982820457</v>
@@ -4963,46 +4963,46 @@
         <v>469694.6058297734</v>
       </c>
       <c r="G71" t="n">
-        <v>523431.8179520136</v>
+        <v>523431.8179520135</v>
       </c>
       <c r="H71" t="n">
-        <v>528365.7247531104</v>
+        <v>528365.7247531103</v>
       </c>
       <c r="I71" t="n">
-        <v>700293.6273884266</v>
+        <v>700293.6273884267</v>
       </c>
       <c r="J71" t="n">
-        <v>595362.3560624025</v>
+        <v>595362.3560624024</v>
       </c>
       <c r="K71" t="n">
-        <v>591555.6091783054</v>
+        <v>591555.6091783055</v>
       </c>
       <c r="L71" t="n">
         <v>650123.2272980596</v>
       </c>
       <c r="M71" t="n">
-        <v>611736.3673089028</v>
+        <v>611736.3673089027</v>
       </c>
       <c r="N71" t="n">
         <v>691367.8427218102</v>
       </c>
       <c r="O71" t="n">
-        <v>834404.1030870606</v>
+        <v>834404.1030870605</v>
       </c>
       <c r="P71" t="n">
-        <v>815827.7580562594</v>
+        <v>815827.7580562595</v>
       </c>
       <c r="Q71" t="n">
-        <v>778275.1712490295</v>
+        <v>778275.1712490293</v>
       </c>
       <c r="R71" t="n">
-        <v>894797.7130711238</v>
+        <v>894797.7130711239</v>
       </c>
       <c r="S71" t="n">
         <v>952138.8716861933</v>
       </c>
       <c r="T71" t="n">
-        <v>965938.5209944909</v>
+        <v>965938.5209944908</v>
       </c>
     </row>
     <row r="72">
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>95768.76282874585</v>
+        <v>95768.76282874586</v>
       </c>
       <c r="D72" t="n">
-        <v>88228.18796672068</v>
+        <v>88228.1879667207</v>
       </c>
       <c r="E72" t="n">
         <v>89097.67352312634</v>
@@ -5045,7 +5045,7 @@
         <v>143538.4610505294</v>
       </c>
       <c r="M72" t="n">
-        <v>131238.982916254</v>
+        <v>131238.9829162541</v>
       </c>
       <c r="N72" t="n">
         <v>130722.5234682253</v>
@@ -5079,28 +5079,28 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>83898.17741941476</v>
+        <v>83898.17741941479</v>
       </c>
       <c r="D73" t="n">
-        <v>78023.30324041196</v>
+        <v>78023.30324041194</v>
       </c>
       <c r="E73" t="n">
-        <v>77901.95337532635</v>
+        <v>77901.95337532638</v>
       </c>
       <c r="F73" t="n">
         <v>70316.28965943704</v>
       </c>
       <c r="G73" t="n">
-        <v>74833.11606185546</v>
+        <v>74833.11606185549</v>
       </c>
       <c r="H73" t="n">
-        <v>99379.03209812626</v>
+        <v>99379.03209812625</v>
       </c>
       <c r="I73" t="n">
         <v>118074.691181818</v>
       </c>
       <c r="J73" t="n">
-        <v>95687.07987636011</v>
+        <v>95687.07987636009</v>
       </c>
       <c r="K73" t="n">
         <v>104154.0538392031</v>
@@ -5115,7 +5115,7 @@
         <v>115460.5307757805</v>
       </c>
       <c r="O73" t="n">
-        <v>174306.8360488748</v>
+        <v>174306.8360488749</v>
       </c>
       <c r="P73" t="n">
         <v>188173.3307573244</v>
@@ -5130,7 +5130,7 @@
         <v>204993.1367061596</v>
       </c>
       <c r="T73" t="n">
-        <v>207250.5043239649</v>
+        <v>207250.504323965</v>
       </c>
     </row>
     <row r="74">
@@ -5146,13 +5146,13 @@
         <v>93605.09823141059</v>
       </c>
       <c r="D74" t="n">
-        <v>88236.26560613484</v>
+        <v>88236.26560613485</v>
       </c>
       <c r="E74" t="n">
-        <v>91138.97985789954</v>
+        <v>91138.97985789953</v>
       </c>
       <c r="F74" t="n">
-        <v>72495.34419723228</v>
+        <v>72495.34419723226</v>
       </c>
       <c r="G74" t="n">
         <v>76478.19582127783</v>
@@ -5167,7 +5167,7 @@
         <v>106880.7670690386</v>
       </c>
       <c r="K74" t="n">
-        <v>100802.1877910939</v>
+        <v>100802.187791094</v>
       </c>
       <c r="L74" t="n">
         <v>116368.3501864196</v>
@@ -5185,7 +5185,7 @@
         <v>203409.2968111393</v>
       </c>
       <c r="Q74" t="n">
-        <v>174966.3810469468</v>
+        <v>174966.3810469469</v>
       </c>
       <c r="R74" t="n">
         <v>227322.628822778</v>
@@ -5216,7 +5216,7 @@
         <v>197.9933830812398</v>
       </c>
       <c r="F75" t="n">
-        <v>173.6107963624545</v>
+        <v>173.6107963624546</v>
       </c>
       <c r="G75" t="n">
         <v>181.517955380365</v>
@@ -5240,13 +5240,13 @@
         <v>223.9594980006029</v>
       </c>
       <c r="N75" t="n">
-        <v>249.707631318085</v>
+        <v>249.7076313180849</v>
       </c>
       <c r="O75" t="n">
         <v>293.7911805518821</v>
       </c>
       <c r="P75" t="n">
-        <v>302.7654622194297</v>
+        <v>302.7654622194298</v>
       </c>
       <c r="Q75" t="n">
         <v>351.6719654594731</v>
@@ -5274,7 +5274,7 @@
         <v>77384.8577343364</v>
       </c>
       <c r="D76" t="n">
-        <v>67681.70942311018</v>
+        <v>67681.70942311019</v>
       </c>
       <c r="E76" t="n">
         <v>63896.01330411385</v>
@@ -5283,7 +5283,7 @@
         <v>62605.12353840657</v>
       </c>
       <c r="G76" t="n">
-        <v>62324.52438795516</v>
+        <v>62324.52438795514</v>
       </c>
       <c r="H76" t="n">
         <v>52329.71815618058</v>
@@ -5295,22 +5295,22 @@
         <v>84108.32060902995</v>
       </c>
       <c r="K76" t="n">
-        <v>86247.72993347538</v>
+        <v>86247.72993347539</v>
       </c>
       <c r="L76" t="n">
-        <v>96388.64154708567</v>
+        <v>96388.64154708569</v>
       </c>
       <c r="M76" t="n">
-        <v>87792.15452412172</v>
+        <v>87792.15452412171</v>
       </c>
       <c r="N76" t="n">
-        <v>94370.19194571514</v>
+        <v>94370.19194571512</v>
       </c>
       <c r="O76" t="n">
         <v>156368.3579294887</v>
       </c>
       <c r="P76" t="n">
-        <v>171647.5690539274</v>
+        <v>171647.5690539275</v>
       </c>
       <c r="Q76" t="n">
         <v>164731.9523726888</v>
@@ -5319,7 +5319,7 @@
         <v>192407.3470829338</v>
       </c>
       <c r="S76" t="n">
-        <v>212628.0625532424</v>
+        <v>212628.0625532423</v>
       </c>
       <c r="T76" t="n">
         <v>222728.8119368664</v>
@@ -5347,7 +5347,7 @@
         <v>2117.212500218904</v>
       </c>
       <c r="G77" t="n">
-        <v>2258.540511822041</v>
+        <v>2258.54051182204</v>
       </c>
       <c r="H77" t="n">
         <v>1839.615522838136</v>
@@ -5496,7 +5496,7 @@
         <v>1466.978349572202</v>
       </c>
       <c r="N79" t="n">
-        <v>1665.379657199655</v>
+        <v>1665.379657199654</v>
       </c>
       <c r="O79" t="n">
         <v>2425.622667177066</v>
@@ -5505,10 +5505,10 @@
         <v>2417.57341171709</v>
       </c>
       <c r="Q79" t="n">
-        <v>2330.749539659785</v>
+        <v>2330.749539659786</v>
       </c>
       <c r="R79" t="n">
-        <v>2744.29296731305</v>
+        <v>2744.292967313051</v>
       </c>
       <c r="S79" t="n">
         <v>2720.088468097784</v>
@@ -5527,10 +5527,10 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>8684.777421722643</v>
+        <v>8684.777421722642</v>
       </c>
       <c r="D80" t="n">
-        <v>5945.897142476737</v>
+        <v>5945.897142476739</v>
       </c>
       <c r="E80" t="n">
         <v>6493.92900837112</v>
@@ -5539,7 +5539,7 @@
         <v>7185.946931660492</v>
       </c>
       <c r="G80" t="n">
-        <v>6972.215009096325</v>
+        <v>6972.215009096324</v>
       </c>
       <c r="H80" t="n">
         <v>11155.49040506891</v>
@@ -5548,7 +5548,7 @@
         <v>14164.55449256631</v>
       </c>
       <c r="J80" t="n">
-        <v>12363.81988444324</v>
+        <v>12363.81988444325</v>
       </c>
       <c r="K80" t="n">
         <v>10637.04647620982</v>
@@ -5566,7 +5566,7 @@
         <v>20219.95236462569</v>
       </c>
       <c r="P80" t="n">
-        <v>26186.56842961539</v>
+        <v>26186.56842961538</v>
       </c>
       <c r="Q80" t="n">
         <v>26903.94224133794</v>
@@ -5575,7 +5575,7 @@
         <v>37394.42089377217</v>
       </c>
       <c r="S80" t="n">
-        <v>40489.30949108575</v>
+        <v>40489.30949108573</v>
       </c>
       <c r="T80" t="n">
         <v>35948.05352000685</v>
@@ -5594,28 +5594,28 @@
         <v>5692.486321764837</v>
       </c>
       <c r="D81" t="n">
-        <v>5459.844544468732</v>
+        <v>5459.844544468731</v>
       </c>
       <c r="E81" t="n">
         <v>5622.082060021568</v>
       </c>
       <c r="F81" t="n">
-        <v>3916.219486140696</v>
+        <v>3916.219486140695</v>
       </c>
       <c r="G81" t="n">
         <v>4142.339099403359</v>
       </c>
       <c r="H81" t="n">
-        <v>5869.517442934251</v>
+        <v>5869.517442934252</v>
       </c>
       <c r="I81" t="n">
-        <v>5672.419453542699</v>
+        <v>5672.4194535427</v>
       </c>
       <c r="J81" t="n">
-        <v>4891.659334440744</v>
+        <v>4891.659334440745</v>
       </c>
       <c r="K81" t="n">
-        <v>5200.79338556065</v>
+        <v>5200.793385560649</v>
       </c>
       <c r="L81" t="n">
         <v>5670.279783463046</v>
@@ -5624,22 +5624,22 @@
         <v>5622.007735598828</v>
       </c>
       <c r="N81" t="n">
-        <v>6140.619459698567</v>
+        <v>6140.619459698566</v>
       </c>
       <c r="O81" t="n">
-        <v>8987.837413212263</v>
+        <v>8987.837413212266</v>
       </c>
       <c r="P81" t="n">
-        <v>9607.528003014533</v>
+        <v>9607.528003014537</v>
       </c>
       <c r="Q81" t="n">
-        <v>6622.164713910438</v>
+        <v>6622.164713910439</v>
       </c>
       <c r="R81" t="n">
         <v>10139.56048451114</v>
       </c>
       <c r="S81" t="n">
-        <v>9649.496565287611</v>
+        <v>9649.496565287607</v>
       </c>
       <c r="T81" t="n">
         <v>10728.87106040379</v>
@@ -5719,7 +5719,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>70872.88212851802</v>
+        <v>70872.882128518</v>
       </c>
       <c r="D83" t="n">
         <v>65225.11919845577</v>
@@ -5758,7 +5758,7 @@
         <v>273660.5339275119</v>
       </c>
       <c r="P83" t="n">
-        <v>289401.7594833496</v>
+        <v>289401.7594833497</v>
       </c>
       <c r="Q83" t="n">
         <v>258102.1219275798</v>
@@ -5770,7 +5770,7 @@
         <v>335561.245659889</v>
       </c>
       <c r="T83" t="n">
-        <v>337670.8489938409</v>
+        <v>337670.8489938408</v>
       </c>
     </row>
     <row r="84">
@@ -5798,10 +5798,10 @@
         <v>17103.14395905229</v>
       </c>
       <c r="H84" t="n">
-        <v>30260.2001337178</v>
+        <v>30260.20013371779</v>
       </c>
       <c r="I84" t="n">
-        <v>29599.29176830143</v>
+        <v>29599.29176830144</v>
       </c>
       <c r="J84" t="n">
         <v>26854.77002462582</v>
@@ -5819,7 +5819,7 @@
         <v>31127.41886456061</v>
       </c>
       <c r="O84" t="n">
-        <v>67833.66795744722</v>
+        <v>67833.66795744724</v>
       </c>
       <c r="P84" t="n">
         <v>65496.13646773206</v>
@@ -5834,7 +5834,7 @@
         <v>87334.18164388461</v>
       </c>
       <c r="T84" t="n">
-        <v>83858.79244197748</v>
+        <v>83858.79244197749</v>
       </c>
     </row>
     <row r="85">
@@ -5865,7 +5865,7 @@
         <v>42743.24095072776</v>
       </c>
       <c r="I85" t="n">
-        <v>91255.91684540198</v>
+        <v>91255.916845402</v>
       </c>
       <c r="J85" t="n">
         <v>72622.92727484525</v>
@@ -5877,7 +5877,7 @@
         <v>93504.00004279155</v>
       </c>
       <c r="M85" t="n">
-        <v>78991.17583108538</v>
+        <v>78991.17583108539</v>
       </c>
       <c r="N85" t="n">
         <v>95600.58511536336</v>
@@ -5895,7 +5895,7 @@
         <v>97236.08434655356</v>
       </c>
       <c r="S85" t="n">
-        <v>93792.19200537563</v>
+        <v>93792.19200537565</v>
       </c>
       <c r="T85" t="n">
         <v>116689.0108568954</v>
@@ -5911,19 +5911,19 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>8484.075837741353</v>
+        <v>8484.075837741351</v>
       </c>
       <c r="D86" t="n">
-        <v>8024.47293069901</v>
+        <v>8024.472930699011</v>
       </c>
       <c r="E86" t="n">
-        <v>7865.325750577516</v>
+        <v>7865.325750577517</v>
       </c>
       <c r="F86" t="n">
-        <v>7088.563060417478</v>
+        <v>7088.563060417477</v>
       </c>
       <c r="G86" t="n">
-        <v>7469.915603383421</v>
+        <v>7469.91560338342</v>
       </c>
       <c r="H86" t="n">
         <v>8702.966921823274</v>
@@ -5953,13 +5953,13 @@
         <v>20447.5636039673</v>
       </c>
       <c r="Q86" t="n">
-        <v>18344.44666957904</v>
+        <v>18344.44666957905</v>
       </c>
       <c r="R86" t="n">
         <v>23945.36845861779</v>
       </c>
       <c r="S86" t="n">
-        <v>24589.47213058792</v>
+        <v>24589.47213058793</v>
       </c>
       <c r="T86" t="n">
         <v>23842.16159301817</v>
@@ -6057,7 +6057,7 @@
         <v>128835.585713122</v>
       </c>
       <c r="I88" t="n">
-        <v>207664.4598281273</v>
+        <v>207664.4598281274</v>
       </c>
       <c r="J88" t="n">
         <v>154496.1277820253</v>
@@ -6072,13 +6072,13 @@
         <v>178823.2691886149</v>
       </c>
       <c r="N88" t="n">
-        <v>209432.2918575</v>
+        <v>209432.2918574999</v>
       </c>
       <c r="O88" t="n">
         <v>262557.5002653496</v>
       </c>
       <c r="P88" t="n">
-        <v>249571.4817127541</v>
+        <v>249571.481712754</v>
       </c>
       <c r="Q88" t="n">
         <v>220471.2017195289</v>
@@ -6090,7 +6090,7 @@
         <v>198992.7000863665</v>
       </c>
       <c r="T88" t="n">
-        <v>252897.429438705</v>
+        <v>252897.4294387049</v>
       </c>
     </row>
     <row r="89">
@@ -6179,7 +6179,7 @@
         <v>8294.603169117923</v>
       </c>
       <c r="G90" t="n">
-        <v>8847.342275450901</v>
+        <v>8847.342275450899</v>
       </c>
       <c r="H90" t="n">
         <v>8892.041071816033</v>
@@ -6215,7 +6215,7 @@
         <v>21614.61033053825</v>
       </c>
       <c r="S90" t="n">
-        <v>25773.2927016996</v>
+        <v>25773.29270169961</v>
       </c>
       <c r="T90" t="n">
         <v>26976.41662467432</v>
@@ -6231,7 +6231,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>631.7093096875409</v>
+        <v>631.7093096875408</v>
       </c>
       <c r="D91" t="n">
         <v>535.6529993314771</v>
@@ -6240,28 +6240,28 @@
         <v>578.672017237358</v>
       </c>
       <c r="F91" t="n">
-        <v>535.1442019924708</v>
+        <v>535.1442019924709</v>
       </c>
       <c r="G91" t="n">
-        <v>614.5845969087687</v>
+        <v>614.5845969087686</v>
       </c>
       <c r="H91" t="n">
         <v>454.0504319617719</v>
       </c>
       <c r="I91" t="n">
-        <v>747.2054818331453</v>
+        <v>747.2054818331455</v>
       </c>
       <c r="J91" t="n">
-        <v>625.9211321558111</v>
+        <v>625.9211321558109</v>
       </c>
       <c r="K91" t="n">
-        <v>652.6213992711695</v>
+        <v>652.6213992711694</v>
       </c>
       <c r="L91" t="n">
-        <v>875.1223102135984</v>
+        <v>875.1223102135986</v>
       </c>
       <c r="M91" t="n">
-        <v>845.0192680782637</v>
+        <v>845.0192680782636</v>
       </c>
       <c r="N91" t="n">
         <v>907.2395080661045</v>
@@ -6270,7 +6270,7 @@
         <v>1176.975438931176</v>
       </c>
       <c r="P91" t="n">
-        <v>1307.338014031053</v>
+        <v>1307.338014031052</v>
       </c>
       <c r="Q91" t="n">
         <v>1152.818394070368</v>
@@ -6307,19 +6307,19 @@
         <v>5341.401425803004</v>
       </c>
       <c r="G92" t="n">
-        <v>6021.51826540117</v>
+        <v>6021.518265401169</v>
       </c>
       <c r="H92" t="n">
-        <v>4889.509034760033</v>
+        <v>4889.509034760034</v>
       </c>
       <c r="I92" t="n">
-        <v>7978.727508043102</v>
+        <v>7978.727508043103</v>
       </c>
       <c r="J92" t="n">
         <v>7260.953750981394</v>
       </c>
       <c r="K92" t="n">
-        <v>7628.096338051059</v>
+        <v>7628.096338051058</v>
       </c>
       <c r="L92" t="n">
         <v>9216.787025262569</v>
@@ -6331,7 +6331,7 @@
         <v>9665.116344213371</v>
       </c>
       <c r="O92" t="n">
-        <v>16803.46173488396</v>
+        <v>16803.46173488395</v>
       </c>
       <c r="P92" t="n">
         <v>14722.5423160868</v>
@@ -6359,19 +6359,19 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>86396.87255521328</v>
+        <v>86396.87255521327</v>
       </c>
       <c r="D93" t="n">
         <v>72524.81691905503</v>
       </c>
       <c r="E93" t="n">
-        <v>80429.74205541433</v>
+        <v>80429.74205541435</v>
       </c>
       <c r="F93" t="n">
         <v>57684.3320248259</v>
       </c>
       <c r="G93" t="n">
-        <v>61545.83571331161</v>
+        <v>61545.8357133116</v>
       </c>
       <c r="H93" t="n">
         <v>119041.2817863026</v>
@@ -6383,13 +6383,13 @@
         <v>86950.25535287146</v>
       </c>
       <c r="K93" t="n">
-        <v>83562.29806089065</v>
+        <v>83562.29806089064</v>
       </c>
       <c r="L93" t="n">
         <v>92289.18036156356</v>
       </c>
       <c r="M93" t="n">
-        <v>88295.29489667871</v>
+        <v>88295.29489667872</v>
       </c>
       <c r="N93" t="n">
         <v>96000.17346634145</v>
@@ -6429,7 +6429,7 @@
         <v>37148.09416247078</v>
       </c>
       <c r="E94" t="n">
-        <v>32785.14949852052</v>
+        <v>32785.14949852053</v>
       </c>
       <c r="F94" t="n">
         <v>25559.97133407023</v>
@@ -6453,22 +6453,22 @@
         <v>36248.23072993801</v>
       </c>
       <c r="M94" t="n">
-        <v>30772.07676865462</v>
+        <v>30772.07676865463</v>
       </c>
       <c r="N94" t="n">
         <v>35627.70533161017</v>
       </c>
       <c r="O94" t="n">
-        <v>51729.71088389138</v>
+        <v>51729.7108838914</v>
       </c>
       <c r="P94" t="n">
-        <v>50077.38809627366</v>
+        <v>50077.38809627365</v>
       </c>
       <c r="Q94" t="n">
-        <v>42950.8896561271</v>
+        <v>42950.88965612711</v>
       </c>
       <c r="R94" t="n">
-        <v>56604.04018248881</v>
+        <v>56604.0401824888</v>
       </c>
       <c r="S94" t="n">
         <v>47590.81293076181</v>
@@ -6487,19 +6487,19 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>43358.20211110294</v>
+        <v>43358.20211110295</v>
       </c>
       <c r="D95" t="n">
-        <v>39447.16692975282</v>
+        <v>39447.16692975281</v>
       </c>
       <c r="E95" t="n">
-        <v>43934.12095538644</v>
+        <v>43934.12095538645</v>
       </c>
       <c r="F95" t="n">
         <v>33847.94978093357</v>
       </c>
       <c r="G95" t="n">
-        <v>38220.34199766163</v>
+        <v>38220.34199766164</v>
       </c>
       <c r="H95" t="n">
         <v>42621.32738669717</v>
@@ -6523,7 +6523,7 @@
         <v>46412.374601462</v>
       </c>
       <c r="O95" t="n">
-        <v>53693.05936674309</v>
+        <v>53693.05936674308</v>
       </c>
       <c r="P95" t="n">
         <v>60515.89121446793</v>
@@ -6551,7 +6551,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>8784.547234056119</v>
+        <v>8784.547234056117</v>
       </c>
       <c r="D96" t="n">
         <v>7068.662772105964</v>
@@ -6587,7 +6587,7 @@
         <v>15367.17885046382</v>
       </c>
       <c r="O96" t="n">
-        <v>27795.45144187255</v>
+        <v>27795.45144187256</v>
       </c>
       <c r="P96" t="n">
         <v>24425.31827521467</v>
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>3079.065125445511</v>
+        <v>3079.06512544551</v>
       </c>
       <c r="D97" t="n">
         <v>3232.395854989443</v>
@@ -6627,7 +6627,7 @@
         <v>2908.624523252932</v>
       </c>
       <c r="G97" t="n">
-        <v>3115.869704217189</v>
+        <v>3115.869704217188</v>
       </c>
       <c r="H97" t="n">
         <v>2925.422521173423</v>
@@ -6645,13 +6645,13 @@
         <v>5839.73317923654</v>
       </c>
       <c r="M97" t="n">
-        <v>5308.740363995932</v>
+        <v>5308.740363995933</v>
       </c>
       <c r="N97" t="n">
-        <v>5423.901351829019</v>
+        <v>5423.901351829018</v>
       </c>
       <c r="O97" t="n">
-        <v>9057.553975122535</v>
+        <v>9057.553975122537</v>
       </c>
       <c r="P97" t="n">
         <v>11245.25792040367</v>
@@ -6679,19 +6679,19 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>6125.343028467961</v>
+        <v>6125.34302846796</v>
       </c>
       <c r="D98" t="n">
-        <v>5845.11916999056</v>
+        <v>5845.119169990559</v>
       </c>
       <c r="E98" t="n">
         <v>5695.990365901437</v>
       </c>
       <c r="F98" t="n">
-        <v>5957.147749025991</v>
+        <v>5957.147749025989</v>
       </c>
       <c r="G98" t="n">
-        <v>5814.25253927587</v>
+        <v>5814.252539275868</v>
       </c>
       <c r="H98" t="n">
         <v>7565.717071908644</v>
@@ -6700,7 +6700,7 @@
         <v>9444.59842106356</v>
       </c>
       <c r="J98" t="n">
-        <v>7458.840438188185</v>
+        <v>7458.840438188184</v>
       </c>
       <c r="K98" t="n">
         <v>8228.234175199097</v>
@@ -6718,13 +6718,13 @@
         <v>18256.91318349875</v>
       </c>
       <c r="P98" t="n">
-        <v>19555.65211045033</v>
+        <v>19555.65211045032</v>
       </c>
       <c r="Q98" t="n">
         <v>17886.82223703994</v>
       </c>
       <c r="R98" t="n">
-        <v>22631.61177174674</v>
+        <v>22631.61177174675</v>
       </c>
       <c r="S98" t="n">
         <v>20401.325541467</v>
@@ -6746,22 +6746,22 @@
         <v>5104.578570502612</v>
       </c>
       <c r="D99" t="n">
-        <v>4302.826805868533</v>
+        <v>4302.826805868534</v>
       </c>
       <c r="E99" t="n">
         <v>5396.437661368856</v>
       </c>
       <c r="F99" t="n">
-        <v>5445.001867880857</v>
+        <v>5445.001867880856</v>
       </c>
       <c r="G99" t="n">
         <v>5811.558387383591</v>
       </c>
       <c r="H99" t="n">
-        <v>6676.748423028575</v>
+        <v>6676.748423028576</v>
       </c>
       <c r="I99" t="n">
-        <v>9642.040801426308</v>
+        <v>9642.04080142631</v>
       </c>
       <c r="J99" t="n">
         <v>8633.516706724209</v>
@@ -6807,13 +6807,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>4189.45614919677</v>
+        <v>4189.456149196769</v>
       </c>
       <c r="D100" t="n">
-        <v>3669.031522025819</v>
+        <v>3669.03152202582</v>
       </c>
       <c r="E100" t="n">
-        <v>4104.923991477652</v>
+        <v>4104.923991477651</v>
       </c>
       <c r="F100" t="n">
         <v>3530.799528291059</v>
@@ -6825,37 +6825,37 @@
         <v>4364.46248308911</v>
       </c>
       <c r="I100" t="n">
-        <v>5451.400127895933</v>
+        <v>5451.400127895931</v>
       </c>
       <c r="J100" t="n">
         <v>4618.264996515595</v>
       </c>
       <c r="K100" t="n">
-        <v>4565.533493121707</v>
+        <v>4565.533493121708</v>
       </c>
       <c r="L100" t="n">
-        <v>5406.628253619232</v>
+        <v>5406.628253619233</v>
       </c>
       <c r="M100" t="n">
         <v>5253.19725401407</v>
       </c>
       <c r="N100" t="n">
-        <v>5556.762469094817</v>
+        <v>5556.762469094818</v>
       </c>
       <c r="O100" t="n">
-        <v>8572.134320355051</v>
+        <v>8572.13432035505</v>
       </c>
       <c r="P100" t="n">
         <v>8599.259258493887</v>
       </c>
       <c r="Q100" t="n">
-        <v>8475.132201076722</v>
+        <v>8475.132201076724</v>
       </c>
       <c r="R100" t="n">
         <v>9625.47026929809</v>
       </c>
       <c r="S100" t="n">
-        <v>9816.485780747635</v>
+        <v>9816.485780747633</v>
       </c>
       <c r="T100" t="n">
         <v>10914.40862448784</v>
@@ -6886,7 +6886,7 @@
         <v>10182.57307758602</v>
       </c>
       <c r="H101" t="n">
-        <v>8801.583502748146</v>
+        <v>8801.583502748148</v>
       </c>
       <c r="I101" t="n">
         <v>16123.64466672855</v>
@@ -6916,7 +6916,7 @@
         <v>23799.99125211065</v>
       </c>
       <c r="R101" t="n">
-        <v>28992.13796701681</v>
+        <v>28992.1379670168</v>
       </c>
       <c r="S101" t="n">
         <v>31269.72474462257</v>
@@ -6938,22 +6938,22 @@
         <v>103609.5045985132</v>
       </c>
       <c r="D102" t="n">
-        <v>90212.29472669451</v>
+        <v>90212.2947266945</v>
       </c>
       <c r="E102" t="n">
         <v>91834.75444705057</v>
       </c>
       <c r="F102" t="n">
-        <v>77136.02094678488</v>
+        <v>77136.02094678489</v>
       </c>
       <c r="G102" t="n">
-        <v>80484.0005528364</v>
+        <v>80484.00055283638</v>
       </c>
       <c r="H102" t="n">
         <v>105389.1428096189</v>
       </c>
       <c r="I102" t="n">
-        <v>124792.6149041934</v>
+        <v>124792.6149041933</v>
       </c>
       <c r="J102" t="n">
         <v>115797.8972920599</v>
@@ -6983,7 +6983,7 @@
         <v>281641.2003245265</v>
       </c>
       <c r="S102" t="n">
-        <v>273343.7600581191</v>
+        <v>273343.7600581192</v>
       </c>
       <c r="T102" t="n">
         <v>285875.5542607956</v>
@@ -7002,7 +7002,7 @@
         <v>1304.583992968562</v>
       </c>
       <c r="D103" t="n">
-        <v>1267.545264217004</v>
+        <v>1267.545264217005</v>
       </c>
       <c r="E103" t="n">
         <v>1250.177337954797</v>
@@ -7029,7 +7029,7 @@
         <v>1847.729190399937</v>
       </c>
       <c r="M103" t="n">
-        <v>1906.363233051567</v>
+        <v>1906.363233051568</v>
       </c>
       <c r="N103" t="n">
         <v>1924.835875387078</v>
@@ -7047,7 +7047,7 @@
         <v>3718.906414287055</v>
       </c>
       <c r="S103" t="n">
-        <v>3388.090267127604</v>
+        <v>3388.090267127605</v>
       </c>
       <c r="T103" t="n">
         <v>3319.762062833984</v>
@@ -7063,13 +7063,13 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>5213.574856628253</v>
+        <v>5213.574856628255</v>
       </c>
       <c r="D104" t="n">
-        <v>5005.404200515179</v>
+        <v>5005.40420051518</v>
       </c>
       <c r="E104" t="n">
-        <v>4795.80128476663</v>
+        <v>4795.801284766628</v>
       </c>
       <c r="F104" t="n">
         <v>4765.331027189261</v>
@@ -7081,13 +7081,13 @@
         <v>4034.947580743314</v>
       </c>
       <c r="I104" t="n">
-        <v>6522.110905290361</v>
+        <v>6522.11090529036</v>
       </c>
       <c r="J104" t="n">
-        <v>5499.520853099835</v>
+        <v>5499.520853099834</v>
       </c>
       <c r="K104" t="n">
-        <v>5859.768443011884</v>
+        <v>5859.768443011883</v>
       </c>
       <c r="L104" t="n">
         <v>6676.381415061484</v>
@@ -7096,7 +7096,7 @@
         <v>6399.041447355558</v>
       </c>
       <c r="N104" t="n">
-        <v>7016.344908138023</v>
+        <v>7016.344908138022</v>
       </c>
       <c r="O104" t="n">
         <v>10071.81639645042</v>
@@ -7105,7 +7105,7 @@
         <v>10037.31627090234</v>
       </c>
       <c r="Q104" t="n">
-        <v>9382.332213108399</v>
+        <v>9382.332213108397</v>
       </c>
       <c r="R104" t="n">
         <v>10603.19663647154</v>
@@ -7127,19 +7127,19 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>6024.453441079386</v>
+        <v>6024.453441079387</v>
       </c>
       <c r="D105" t="n">
         <v>5533.042087254357</v>
       </c>
       <c r="E105" t="n">
-        <v>5024.783809816568</v>
+        <v>5024.783809816569</v>
       </c>
       <c r="F105" t="n">
         <v>5007.816072975985</v>
       </c>
       <c r="G105" t="n">
-        <v>5214.779401362021</v>
+        <v>5214.779401362022</v>
       </c>
       <c r="H105" t="n">
         <v>5224.240073475948</v>
@@ -7148,31 +7148,31 @@
         <v>8315.698721591669</v>
       </c>
       <c r="J105" t="n">
-        <v>7309.801295563091</v>
+        <v>7309.80129556309</v>
       </c>
       <c r="K105" t="n">
-        <v>7002.475304749536</v>
+        <v>7002.475304749537</v>
       </c>
       <c r="L105" t="n">
         <v>7775.550510131628</v>
       </c>
       <c r="M105" t="n">
-        <v>7815.656802088889</v>
+        <v>7815.656802088888</v>
       </c>
       <c r="N105" t="n">
-        <v>8282.490919225173</v>
+        <v>8282.490919225174</v>
       </c>
       <c r="O105" t="n">
         <v>12223.82788032235</v>
       </c>
       <c r="P105" t="n">
-        <v>13738.72553180799</v>
+        <v>13738.72553180798</v>
       </c>
       <c r="Q105" t="n">
         <v>12218.83426413098</v>
       </c>
       <c r="R105" t="n">
-        <v>16042.2366814046</v>
+        <v>16042.23668140461</v>
       </c>
       <c r="S105" t="n">
         <v>15330.15154699679</v>
@@ -7197,7 +7197,7 @@
         <v>14713.95500606572</v>
       </c>
       <c r="E106" t="n">
-        <v>17248.67683137138</v>
+        <v>17248.67683137139</v>
       </c>
       <c r="F106" t="n">
         <v>13840.22208331001</v>
@@ -7233,7 +7233,7 @@
         <v>30480.96233751464</v>
       </c>
       <c r="Q106" t="n">
-        <v>24927.7863816056</v>
+        <v>24927.78638160561</v>
       </c>
       <c r="R106" t="n">
         <v>30932.78601920179</v>
@@ -7325,49 +7325,49 @@
         <v>32034.11500566375</v>
       </c>
       <c r="E108" t="n">
-        <v>32564.94458821888</v>
+        <v>32564.94458821889</v>
       </c>
       <c r="F108" t="n">
-        <v>31692.86193430766</v>
+        <v>31692.86193430767</v>
       </c>
       <c r="G108" t="n">
         <v>32910.22461491478</v>
       </c>
       <c r="H108" t="n">
-        <v>39359.19926141191</v>
+        <v>39359.19926141189</v>
       </c>
       <c r="I108" t="n">
-        <v>49843.721195172</v>
+        <v>49843.72119517199</v>
       </c>
       <c r="J108" t="n">
-        <v>43715.51590427365</v>
+        <v>43715.51590427364</v>
       </c>
       <c r="K108" t="n">
-        <v>43518.56123920645</v>
+        <v>43518.56123920644</v>
       </c>
       <c r="L108" t="n">
-        <v>48672.05856637616</v>
+        <v>48672.05856637615</v>
       </c>
       <c r="M108" t="n">
         <v>48474.43735373214</v>
       </c>
       <c r="N108" t="n">
-        <v>51313.88521901445</v>
+        <v>51313.88521901446</v>
       </c>
       <c r="O108" t="n">
-        <v>78790.38294220771</v>
+        <v>78790.3829422077</v>
       </c>
       <c r="P108" t="n">
-        <v>85542.43591437943</v>
+        <v>85542.43591437944</v>
       </c>
       <c r="Q108" t="n">
-        <v>75173.50419218447</v>
+        <v>75173.50419218444</v>
       </c>
       <c r="R108" t="n">
         <v>95050.67206291234</v>
       </c>
       <c r="S108" t="n">
-        <v>84460.78296961419</v>
+        <v>84460.78296961417</v>
       </c>
       <c r="T108" t="n">
         <v>97756.40121650985</v>
@@ -7450,7 +7450,7 @@
         <v>7327.623729355081</v>
       </c>
       <c r="D110" t="n">
-        <v>6705.872776119857</v>
+        <v>6705.872776119858</v>
       </c>
       <c r="E110" t="n">
         <v>5587.125845166142</v>
@@ -7459,7 +7459,7 @@
         <v>5860.255529864155</v>
       </c>
       <c r="G110" t="n">
-        <v>7039.36349099608</v>
+        <v>7039.363490996079</v>
       </c>
       <c r="H110" t="n">
         <v>6864.653457602612</v>
@@ -7468,7 +7468,7 @@
         <v>10057.97888685292</v>
       </c>
       <c r="J110" t="n">
-        <v>8181.881102475866</v>
+        <v>8181.881102475865</v>
       </c>
       <c r="K110" t="n">
         <v>9037.730518142376</v>
@@ -7498,7 +7498,7 @@
         <v>27701.16680840332</v>
       </c>
       <c r="T110" t="n">
-        <v>21119.95872215497</v>
+        <v>21119.95872215496</v>
       </c>
     </row>
     <row r="111">
@@ -7529,7 +7529,7 @@
         <v>189757.1972338082</v>
       </c>
       <c r="I111" t="n">
-        <v>211691.5745184987</v>
+        <v>211691.5745184986</v>
       </c>
       <c r="J111" t="n">
         <v>175932.5839781592</v>
@@ -7547,10 +7547,10 @@
         <v>194598.5780600828</v>
       </c>
       <c r="O111" t="n">
-        <v>312874.2781435622</v>
+        <v>312874.2781435623</v>
       </c>
       <c r="P111" t="n">
-        <v>305838.5169295752</v>
+        <v>305838.5169295751</v>
       </c>
       <c r="Q111" t="n">
         <v>295454.8705040492</v>
@@ -7559,10 +7559,10 @@
         <v>341989.7937847102</v>
       </c>
       <c r="S111" t="n">
-        <v>373025.9593631944</v>
+        <v>373025.9593631942</v>
       </c>
       <c r="T111" t="n">
-        <v>372207.9032097087</v>
+        <v>372207.9032097088</v>
       </c>
     </row>
     <row r="112">
@@ -7602,13 +7602,13 @@
         <v>10629.17404174542</v>
       </c>
       <c r="L112" t="n">
-        <v>11922.28668750986</v>
+        <v>11922.28668750987</v>
       </c>
       <c r="M112" t="n">
         <v>12589.18076027874</v>
       </c>
       <c r="N112" t="n">
-        <v>12279.31138406369</v>
+        <v>12279.3113840637</v>
       </c>
       <c r="O112" t="n">
         <v>20256.82529156206</v>
@@ -7617,7 +7617,7 @@
         <v>18694.43737873261</v>
       </c>
       <c r="Q112" t="n">
-        <v>20896.33393450371</v>
+        <v>20896.33393450372</v>
       </c>
       <c r="R112" t="n">
         <v>22228.16233035947</v>
@@ -7654,13 +7654,13 @@
         <v>2453.570786696789</v>
       </c>
       <c r="H113" t="n">
-        <v>4614.354221840752</v>
+        <v>4614.354221840751</v>
       </c>
       <c r="I113" t="n">
         <v>4319.189909375712</v>
       </c>
       <c r="J113" t="n">
-        <v>3769.520049941989</v>
+        <v>3769.520049941988</v>
       </c>
       <c r="K113" t="n">
         <v>3523.305262286871</v>
@@ -7690,7 +7690,7 @@
         <v>11202.47037510032</v>
       </c>
       <c r="T113" t="n">
-        <v>9722.268471256668</v>
+        <v>9722.268471256666</v>
       </c>
     </row>
     <row r="114">
@@ -7724,10 +7724,10 @@
         <v>1061.852416226687</v>
       </c>
       <c r="J114" t="n">
-        <v>887.5343072155517</v>
+        <v>887.5343072155518</v>
       </c>
       <c r="K114" t="n">
-        <v>977.787753816663</v>
+        <v>977.7877538166629</v>
       </c>
       <c r="L114" t="n">
         <v>1111.644052314003</v>
@@ -7779,7 +7779,7 @@
         <v>9494.265905465576</v>
       </c>
       <c r="G115" t="n">
-        <v>10079.83992447403</v>
+        <v>10079.83992447402</v>
       </c>
       <c r="H115" t="n">
         <v>11227.33122567015</v>
@@ -7831,7 +7831,7 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>3941.535886737268</v>
+        <v>3941.535886737269</v>
       </c>
       <c r="D116" t="n">
         <v>3580.92642797557</v>
@@ -7840,10 +7840,10 @@
         <v>3724.166041185637</v>
       </c>
       <c r="F116" t="n">
-        <v>3274.863872802145</v>
+        <v>3274.863872802144</v>
       </c>
       <c r="G116" t="n">
-        <v>3516.379978933588</v>
+        <v>3516.379978933589</v>
       </c>
       <c r="H116" t="n">
         <v>3576.397459246598</v>
@@ -7861,25 +7861,25 @@
         <v>4430.16399059618</v>
       </c>
       <c r="M116" t="n">
-        <v>4440.107598007254</v>
+        <v>4440.107598007255</v>
       </c>
       <c r="N116" t="n">
-        <v>4756.042521673461</v>
+        <v>4756.042521673462</v>
       </c>
       <c r="O116" t="n">
         <v>6845.094769519583</v>
       </c>
       <c r="P116" t="n">
-        <v>6848.958313465004</v>
+        <v>6848.958313465003</v>
       </c>
       <c r="Q116" t="n">
-        <v>6664.022206451391</v>
+        <v>6664.022206451392</v>
       </c>
       <c r="R116" t="n">
         <v>7214.085762096591</v>
       </c>
       <c r="S116" t="n">
-        <v>7389.958806282384</v>
+        <v>7389.958806282385</v>
       </c>
       <c r="T116" t="n">
         <v>8417.134267244004</v>
@@ -7983,13 +7983,13 @@
         <v>360.8606480780364</v>
       </c>
       <c r="K118" t="n">
-        <v>315.1137675826474</v>
+        <v>315.1137675826475</v>
       </c>
       <c r="L118" t="n">
         <v>389.8754977332306</v>
       </c>
       <c r="M118" t="n">
-        <v>413.8457757023843</v>
+        <v>413.8457757023842</v>
       </c>
       <c r="N118" t="n">
         <v>423.9945078628102</v>
@@ -7998,7 +7998,7 @@
         <v>635.2411460291239</v>
       </c>
       <c r="P118" t="n">
-        <v>759.5810111517044</v>
+        <v>759.5810111517045</v>
       </c>
       <c r="Q118" t="n">
         <v>731.6307583371779</v>
@@ -8029,10 +8029,10 @@
         <v>18110.96751639579</v>
       </c>
       <c r="E119" t="n">
-        <v>20020.02994733141</v>
+        <v>20020.02994733142</v>
       </c>
       <c r="F119" t="n">
-        <v>23087.00637260062</v>
+        <v>23087.00637260063</v>
       </c>
       <c r="G119" t="n">
         <v>24148.18530757763</v>
@@ -8041,22 +8041,22 @@
         <v>23205.57583055564</v>
       </c>
       <c r="I119" t="n">
-        <v>41177.27838458781</v>
+        <v>41177.27838458782</v>
       </c>
       <c r="J119" t="n">
-        <v>35227.32556761428</v>
+        <v>35227.32556761429</v>
       </c>
       <c r="K119" t="n">
         <v>37008.34944331378</v>
       </c>
       <c r="L119" t="n">
-        <v>44297.77366350367</v>
+        <v>44297.77366350368</v>
       </c>
       <c r="M119" t="n">
         <v>40576.73858950646</v>
       </c>
       <c r="N119" t="n">
-        <v>44799.32773746343</v>
+        <v>44799.32773746344</v>
       </c>
       <c r="O119" t="n">
         <v>66692.72203301117</v>
@@ -8065,13 +8065,13 @@
         <v>70691.71060014998</v>
       </c>
       <c r="Q119" t="n">
-        <v>60735.05338601351</v>
+        <v>60735.0533860135</v>
       </c>
       <c r="R119" t="n">
-        <v>76795.88164011513</v>
+        <v>76795.88164011511</v>
       </c>
       <c r="S119" t="n">
-        <v>76637.55715227754</v>
+        <v>76637.55715227756</v>
       </c>
       <c r="T119" t="n">
         <v>78426.37340611294</v>
@@ -8090,7 +8090,7 @@
         <v>4267420.212482836</v>
       </c>
       <c r="D120" t="n">
-        <v>3692003.52696731</v>
+        <v>3692003.526967309</v>
       </c>
       <c r="E120" t="n">
         <v>3932868.737471241</v>
@@ -8099,25 +8099,25 @@
         <v>3700690.684351689</v>
       </c>
       <c r="G120" t="n">
-        <v>3755427.59475541</v>
+        <v>3755427.594755411</v>
       </c>
       <c r="H120" t="n">
         <v>5351820.855313172</v>
       </c>
       <c r="I120" t="n">
-        <v>6486419.927325245</v>
+        <v>6486419.927325248</v>
       </c>
       <c r="J120" t="n">
-        <v>5457146.106298958</v>
+        <v>5457146.106298956</v>
       </c>
       <c r="K120" t="n">
-        <v>5387463.331420559</v>
+        <v>5387463.331420558</v>
       </c>
       <c r="L120" t="n">
-        <v>7877373.589045805</v>
+        <v>7877373.589045806</v>
       </c>
       <c r="M120" t="n">
-        <v>7600408.127375433</v>
+        <v>7600408.127375434</v>
       </c>
       <c r="N120" t="n">
         <v>7019564.134074812</v>
@@ -8236,13 +8236,13 @@
         <v>2364.845272365332</v>
       </c>
       <c r="J122" t="n">
-        <v>2208.541821058179</v>
+        <v>2208.541821058178</v>
       </c>
       <c r="K122" t="n">
         <v>2406.689647147517</v>
       </c>
       <c r="L122" t="n">
-        <v>2479.33461525286</v>
+        <v>2479.334615252861</v>
       </c>
       <c r="M122" t="n">
         <v>2196.695622847923</v>
@@ -8303,7 +8303,7 @@
         <v>40122.9050476359</v>
       </c>
       <c r="K123" t="n">
-        <v>40117.47196237407</v>
+        <v>40117.47196237406</v>
       </c>
       <c r="L123" t="n">
         <v>47464.86402729261</v>
@@ -8318,10 +8318,10 @@
         <v>78633.9891625389</v>
       </c>
       <c r="P123" t="n">
-        <v>81495.74521267862</v>
+        <v>81495.74521267864</v>
       </c>
       <c r="Q123" t="n">
-        <v>89950.06428527882</v>
+        <v>89950.06428527883</v>
       </c>
       <c r="R123" t="n">
         <v>102615.4005262437</v>
@@ -8330,7 +8330,7 @@
         <v>122829.290064914</v>
       </c>
       <c r="T123" t="n">
-        <v>112021.3543906398</v>
+        <v>112021.3543906397</v>
       </c>
     </row>
     <row r="124">
@@ -8349,13 +8349,13 @@
         <v>35919.97623071459</v>
       </c>
       <c r="E124" t="n">
-        <v>36537.50823949587</v>
+        <v>36537.50823949588</v>
       </c>
       <c r="F124" t="n">
         <v>35043.56181850164</v>
       </c>
       <c r="G124" t="n">
-        <v>39885.6576263709</v>
+        <v>39885.65762637089</v>
       </c>
       <c r="H124" t="n">
         <v>35745.17628791033</v>
@@ -8364,10 +8364,10 @@
         <v>48675.65801892959</v>
       </c>
       <c r="J124" t="n">
-        <v>41041.82428299373</v>
+        <v>41041.82428299374</v>
       </c>
       <c r="K124" t="n">
-        <v>48240.92216287436</v>
+        <v>48240.92216287437</v>
       </c>
       <c r="L124" t="n">
         <v>50301.7209582366</v>
@@ -8379,7 +8379,7 @@
         <v>53336.86779284452</v>
       </c>
       <c r="O124" t="n">
-        <v>80125.12911266924</v>
+        <v>80125.12911266925</v>
       </c>
       <c r="P124" t="n">
         <v>85928.50661838258</v>
@@ -8394,7 +8394,7 @@
         <v>84540.90107701902</v>
       </c>
       <c r="T124" t="n">
-        <v>84191.71624713429</v>
+        <v>84191.71624713427</v>
       </c>
     </row>
     <row r="125">
@@ -8410,7 +8410,7 @@
         <v>158794.3032092349</v>
       </c>
       <c r="D125" t="n">
-        <v>147249.4432341667</v>
+        <v>147249.4432341666</v>
       </c>
       <c r="E125" t="n">
         <v>134199.451238839</v>
@@ -8425,7 +8425,7 @@
         <v>101164.1441891696</v>
       </c>
       <c r="I125" t="n">
-        <v>214413.6986243719</v>
+        <v>214413.698624372</v>
       </c>
       <c r="J125" t="n">
         <v>168036.3603331477</v>
@@ -8446,16 +8446,16 @@
         <v>306723.045054519</v>
       </c>
       <c r="P125" t="n">
-        <v>317418.9268296519</v>
+        <v>317418.9268296518</v>
       </c>
       <c r="Q125" t="n">
-        <v>308006.3996998453</v>
+        <v>308006.3996998454</v>
       </c>
       <c r="R125" t="n">
-        <v>327930.9186391365</v>
+        <v>327930.9186391364</v>
       </c>
       <c r="S125" t="n">
-        <v>345545.8146581608</v>
+        <v>345545.8146581607</v>
       </c>
       <c r="T125" t="n">
         <v>427424.7942186628</v>
@@ -8556,7 +8556,7 @@
         <v>29251.83733620387</v>
       </c>
       <c r="J127" t="n">
-        <v>24669.96490145554</v>
+        <v>24669.96490145555</v>
       </c>
       <c r="K127" t="n">
         <v>25332.38702313889</v>
@@ -8568,13 +8568,13 @@
         <v>29577.95935277753</v>
       </c>
       <c r="N127" t="n">
-        <v>30617.85037708867</v>
+        <v>30617.85037708866</v>
       </c>
       <c r="O127" t="n">
         <v>59097.51365613252</v>
       </c>
       <c r="P127" t="n">
-        <v>61996.80532412359</v>
+        <v>61996.8053241236</v>
       </c>
       <c r="Q127" t="n">
         <v>70611.61515823443</v>
@@ -8586,7 +8586,7 @@
         <v>89541.22746355283</v>
       </c>
       <c r="T127" t="n">
-        <v>91164.54506493286</v>
+        <v>91164.54506493287</v>
       </c>
     </row>
     <row r="128">
@@ -8647,7 +8647,7 @@
         <v>30508.80660706591</v>
       </c>
       <c r="S128" t="n">
-        <v>33100.57355866473</v>
+        <v>33100.57355866472</v>
       </c>
       <c r="T128" t="n">
         <v>29579.86215766029</v>
@@ -8672,7 +8672,7 @@
         <v>3198.028989603305</v>
       </c>
       <c r="F129" t="n">
-        <v>2907.979796172253</v>
+        <v>2907.979796172254</v>
       </c>
       <c r="G129" t="n">
         <v>2927.36268782764</v>
@@ -8687,16 +8687,16 @@
         <v>4474.469022543828</v>
       </c>
       <c r="K129" t="n">
-        <v>4348.393330232382</v>
+        <v>4348.393330232383</v>
       </c>
       <c r="L129" t="n">
-        <v>5188.77220298204</v>
+        <v>5188.772202982039</v>
       </c>
       <c r="M129" t="n">
         <v>4898.949995462825</v>
       </c>
       <c r="N129" t="n">
-        <v>4990.307081876485</v>
+        <v>4990.307081876484</v>
       </c>
       <c r="O129" t="n">
         <v>8507.170936315282</v>
@@ -8730,19 +8730,19 @@
         <v>2528.188175274881</v>
       </c>
       <c r="D130" t="n">
-        <v>2564.680002843204</v>
+        <v>2564.680002843205</v>
       </c>
       <c r="E130" t="n">
         <v>2566.494902818928</v>
       </c>
       <c r="F130" t="n">
-        <v>2359.73902266008</v>
+        <v>2359.739022660081</v>
       </c>
       <c r="G130" t="n">
         <v>2292.492979325602</v>
       </c>
       <c r="H130" t="n">
-        <v>2339.291853204812</v>
+        <v>2339.291853204811</v>
       </c>
       <c r="I130" t="n">
         <v>3845.864001194821</v>
@@ -8751,10 +8751,10 @@
         <v>3316.092356656391</v>
       </c>
       <c r="K130" t="n">
-        <v>3780.708813033656</v>
+        <v>3780.708813033657</v>
       </c>
       <c r="L130" t="n">
-        <v>3310.418097585594</v>
+        <v>3310.418097585595</v>
       </c>
       <c r="M130" t="n">
         <v>3596.871006522888</v>
@@ -8766,10 +8766,10 @@
         <v>7475.858996025251</v>
       </c>
       <c r="P130" t="n">
-        <v>7521.188256755033</v>
+        <v>7521.188256755032</v>
       </c>
       <c r="Q130" t="n">
-        <v>6473.905965084679</v>
+        <v>6473.905965084678</v>
       </c>
       <c r="R130" t="n">
         <v>8668.121969328948</v>
@@ -8778,7 +8778,7 @@
         <v>8085.926246997084</v>
       </c>
       <c r="T130" t="n">
-        <v>9153.306539964711</v>
+        <v>9153.306539964709</v>
       </c>
     </row>
     <row r="131">
@@ -8794,13 +8794,13 @@
         <v>8331.604124017231</v>
       </c>
       <c r="D131" t="n">
-        <v>7654.166342736235</v>
+        <v>7654.166342736236</v>
       </c>
       <c r="E131" t="n">
         <v>8026.703355693684</v>
       </c>
       <c r="F131" t="n">
-        <v>7881.472406420872</v>
+        <v>7881.472406420873</v>
       </c>
       <c r="G131" t="n">
         <v>8413.639607235758</v>
@@ -8818,7 +8818,7 @@
         <v>10663.5819346938</v>
       </c>
       <c r="L131" t="n">
-        <v>13167.70155475707</v>
+        <v>13167.70155475706</v>
       </c>
       <c r="M131" t="n">
         <v>12803.09973959779</v>
@@ -8827,7 +8827,7 @@
         <v>13581.74460770136</v>
       </c>
       <c r="O131" t="n">
-        <v>21412.29382328602</v>
+        <v>21412.29382328601</v>
       </c>
       <c r="P131" t="n">
         <v>21552.36886611649</v>
@@ -8839,7 +8839,7 @@
         <v>25421.87361864997</v>
       </c>
       <c r="S131" t="n">
-        <v>25298.74576133278</v>
+        <v>25298.74576133277</v>
       </c>
       <c r="T131" t="n">
         <v>26884.19525433863</v>
@@ -8855,16 +8855,16 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>6167.530477387489</v>
+        <v>6167.53047738749</v>
       </c>
       <c r="D132" t="n">
-        <v>4668.3507574077</v>
+        <v>4668.350757407701</v>
       </c>
       <c r="E132" t="n">
         <v>4402.541406466108</v>
       </c>
       <c r="F132" t="n">
-        <v>4555.438356603561</v>
+        <v>4555.438356603562</v>
       </c>
       <c r="G132" t="n">
         <v>4673.543195829319</v>
@@ -8873,22 +8873,22 @@
         <v>6453.277669090112</v>
       </c>
       <c r="I132" t="n">
-        <v>8079.299886127703</v>
+        <v>8079.299886127702</v>
       </c>
       <c r="J132" t="n">
         <v>6473.164555662055</v>
       </c>
       <c r="K132" t="n">
-        <v>6833.90357613068</v>
+        <v>6833.903576130681</v>
       </c>
       <c r="L132" t="n">
         <v>7644.900940762498</v>
       </c>
       <c r="M132" t="n">
-        <v>7160.083960528284</v>
+        <v>7160.083960528283</v>
       </c>
       <c r="N132" t="n">
-        <v>7457.138216061837</v>
+        <v>7457.138216061836</v>
       </c>
       <c r="O132" t="n">
         <v>11670.21204105382</v>
@@ -8925,19 +8925,19 @@
         <v>30968.23008995575</v>
       </c>
       <c r="E133" t="n">
-        <v>36860.394446178</v>
+        <v>36860.39444617799</v>
       </c>
       <c r="F133" t="n">
         <v>39908.47312066852</v>
       </c>
       <c r="G133" t="n">
-        <v>43243.84740577534</v>
+        <v>43243.84740577533</v>
       </c>
       <c r="H133" t="n">
         <v>42636.3052449793</v>
       </c>
       <c r="I133" t="n">
-        <v>68165.43998094177</v>
+        <v>68165.43998094178</v>
       </c>
       <c r="J133" t="n">
         <v>59042.93774077069</v>
@@ -8992,7 +8992,7 @@
         <v>229.2324771427699</v>
       </c>
       <c r="F134" t="n">
-        <v>192.8493513532203</v>
+        <v>192.8493513532204</v>
       </c>
       <c r="G134" t="n">
         <v>206.2853187402058</v>
@@ -9019,7 +9019,7 @@
         <v>268.0923448653182</v>
       </c>
       <c r="O134" t="n">
-        <v>245.1272363225394</v>
+        <v>245.1272363225395</v>
       </c>
       <c r="P134" t="n">
         <v>351.4307027221786</v>
@@ -9028,7 +9028,7 @@
         <v>251.3447395060146</v>
       </c>
       <c r="R134" t="n">
-        <v>335.5736639472629</v>
+        <v>335.5736639472628</v>
       </c>
       <c r="S134" t="n">
         <v>264.8198307439317</v>
@@ -9047,10 +9047,10 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>2370.707968205449</v>
+        <v>2370.70796820545</v>
       </c>
       <c r="D135" t="n">
-        <v>2256.558110579527</v>
+        <v>2256.558110579526</v>
       </c>
       <c r="E135" t="n">
         <v>1961.483653053743</v>
@@ -9065,7 +9065,7 @@
         <v>1503.457376896503</v>
       </c>
       <c r="I135" t="n">
-        <v>2161.466882358293</v>
+        <v>2161.466882358292</v>
       </c>
       <c r="J135" t="n">
         <v>1906.39671931342</v>
@@ -9083,13 +9083,13 @@
         <v>2706.848010933832</v>
       </c>
       <c r="O135" t="n">
-        <v>4644.057428260493</v>
+        <v>4644.057428260492</v>
       </c>
       <c r="P135" t="n">
         <v>4537.788767827682</v>
       </c>
       <c r="Q135" t="n">
-        <v>4861.386305203382</v>
+        <v>4861.386305203383</v>
       </c>
       <c r="R135" t="n">
         <v>5496.08846969656</v>
@@ -9199,13 +9199,13 @@
         <v>1792.222266827003</v>
       </c>
       <c r="K137" t="n">
-        <v>2452.253980978643</v>
+        <v>2452.253980978644</v>
       </c>
       <c r="L137" t="n">
         <v>3005.826901510315</v>
       </c>
       <c r="M137" t="n">
-        <v>3079.244002188056</v>
+        <v>3079.244002188057</v>
       </c>
       <c r="N137" t="n">
         <v>2938.303311569499</v>
@@ -9214,7 +9214,7 @@
         <v>3973.631329915356</v>
       </c>
       <c r="P137" t="n">
-        <v>4071.19888084906</v>
+        <v>4071.198880849059</v>
       </c>
       <c r="Q137" t="n">
         <v>3337.595153352687</v>
@@ -9239,10 +9239,10 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>979.3604082560887</v>
+        <v>979.3604082560889</v>
       </c>
       <c r="D138" t="n">
-        <v>990.5358062188261</v>
+        <v>990.5358062188262</v>
       </c>
       <c r="E138" t="n">
         <v>442.9796611965401</v>
@@ -9266,16 +9266,16 @@
         <v>1287.654517047979</v>
       </c>
       <c r="L138" t="n">
-        <v>1464.881147900442</v>
+        <v>1464.881147900443</v>
       </c>
       <c r="M138" t="n">
-        <v>617.8098223220082</v>
+        <v>617.8098223220084</v>
       </c>
       <c r="N138" t="n">
         <v>1431.72237780294</v>
       </c>
       <c r="O138" t="n">
-        <v>2550.164618758578</v>
+        <v>2550.164618758579</v>
       </c>
       <c r="P138" t="n">
         <v>1000.573282580817</v>
@@ -9290,7 +9290,7 @@
         <v>3085.733146441479</v>
       </c>
       <c r="T138" t="n">
-        <v>2858.20591342544</v>
+        <v>2858.205913425439</v>
       </c>
     </row>
     <row r="139">
@@ -9339,13 +9339,13 @@
         <v>1769.808039241204</v>
       </c>
       <c r="O139" t="n">
-        <v>3161.460195214971</v>
+        <v>3161.46019521497</v>
       </c>
       <c r="P139" t="n">
         <v>1642.721100923769</v>
       </c>
       <c r="Q139" t="n">
-        <v>3241.046567717212</v>
+        <v>3241.046567717211</v>
       </c>
       <c r="R139" t="n">
         <v>1655.191253783246</v>
